--- a/research/traditional_assets/database/data/argentina/argentina_construction_supplies.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_construction_supplies.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="base_harg" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.45</v>
+        <v>0.3779999999999999</v>
       </c>
       <c r="E2">
-        <v>0.5760000000000001</v>
+        <v>0.23</v>
       </c>
       <c r="G2">
-        <v>0.4607276436586195</v>
+        <v>0.5286940804338003</v>
       </c>
       <c r="H2">
-        <v>0.4607276436586195</v>
+        <v>0.5286940804338003</v>
       </c>
       <c r="I2">
-        <v>0.1904114246854811</v>
+        <v>0.1107094441934026</v>
       </c>
       <c r="J2">
-        <v>0.1671117930893517</v>
+        <v>0.05535472209670131</v>
       </c>
       <c r="K2">
-        <v>61.6</v>
+        <v>14.7</v>
       </c>
       <c r="L2">
-        <v>0.2094525671540292</v>
+        <v>0.06642566651604156</v>
       </c>
       <c r="M2">
-        <v>13.4</v>
+        <v>45.5</v>
       </c>
       <c r="N2">
-        <v>0.02289033139733516</v>
+        <v>0.06966773847802786</v>
       </c>
       <c r="O2">
-        <v>0.2175324675324675</v>
+        <v>3.095238095238095</v>
       </c>
       <c r="P2">
-        <v>13.4</v>
+        <v>45.5</v>
       </c>
       <c r="Q2">
-        <v>0.02289033139733516</v>
+        <v>0.06966773847802786</v>
       </c>
       <c r="R2">
-        <v>0.2175324675324675</v>
+        <v>3.095238095238095</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,70 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>53.1</v>
+        <v>41.2</v>
       </c>
       <c r="V2">
-        <v>0.09070720874615648</v>
+        <v>0.06308375440208237</v>
       </c>
       <c r="W2">
-        <v>0.2030323005932762</v>
+        <v>0.03509190737646217</v>
       </c>
       <c r="X2">
-        <v>0.289789045337049</v>
+        <v>0.1973685288318937</v>
       </c>
       <c r="Y2">
-        <v>-0.08675674474377273</v>
+        <v>-0.1622766214554315</v>
       </c>
       <c r="Z2">
-        <v>1.242973669751913</v>
+        <v>0.6034823632074831</v>
       </c>
       <c r="AA2">
-        <v>0.2077155587150939</v>
+        <v>0.03340559850561078</v>
       </c>
       <c r="AB2">
-        <v>0.2895365083373939</v>
+        <v>0.1973018945581404</v>
       </c>
       <c r="AC2">
-        <v>-0.08182094962229999</v>
+        <v>-0.1638962960525296</v>
       </c>
       <c r="AD2">
-        <v>0.905</v>
+        <v>0.549</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.905</v>
+        <v>0.549</v>
       </c>
       <c r="AG2">
-        <v>-52.195</v>
+        <v>-40.651</v>
       </c>
       <c r="AH2">
-        <v>0.001543565209234102</v>
+        <v>0.0008399003134709913</v>
       </c>
       <c r="AI2">
-        <v>0.002155762794630841</v>
+        <v>0.001349394984379954</v>
       </c>
       <c r="AJ2">
-        <v>-0.09788917958383737</v>
+        <v>-0.06637450628542131</v>
       </c>
       <c r="AK2">
-        <v>-0.142335119510233</v>
+        <v>-0.1111749245861468</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AM2">
-        <v>-10.3</v>
+        <v>-18.8</v>
       </c>
       <c r="AN2">
-        <v>0.01193931398416887</v>
+        <v>0.01316546762589928</v>
+      </c>
+      <c r="AO2">
+        <v>7.65625</v>
       </c>
       <c r="AP2">
-        <v>-0.6885883905013193</v>
+        <v>-0.9748441247002398</v>
       </c>
       <c r="AQ2">
-        <v>-5.436893203883495</v>
+        <v>-1.303191489361702</v>
       </c>
     </row>
     <row r="3">
@@ -719,118 +724,8893 @@
         </is>
       </c>
       <c r="D3">
+        <v>0.3779999999999999</v>
+      </c>
+      <c r="E3">
+        <v>0.23</v>
+      </c>
+      <c r="G3">
+        <v>0.5286940804338003</v>
+      </c>
+      <c r="H3">
+        <v>0.5286940804338003</v>
+      </c>
+      <c r="I3">
+        <v>0.1107094441934026</v>
+      </c>
+      <c r="J3">
+        <v>0.05535472209670131</v>
+      </c>
+      <c r="K3">
+        <v>14.7</v>
+      </c>
+      <c r="L3">
+        <v>0.06642566651604156</v>
+      </c>
+      <c r="M3">
+        <v>45.5</v>
+      </c>
+      <c r="N3">
+        <v>0.06966773847802786</v>
+      </c>
+      <c r="O3">
+        <v>3.095238095238095</v>
+      </c>
+      <c r="P3">
+        <v>45.5</v>
+      </c>
+      <c r="Q3">
+        <v>0.06966773847802786</v>
+      </c>
+      <c r="R3">
+        <v>3.095238095238095</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>41.2</v>
+      </c>
+      <c r="V3">
+        <v>0.06308375440208237</v>
+      </c>
+      <c r="W3">
+        <v>0.03509190737646217</v>
+      </c>
+      <c r="X3">
+        <v>0.1973685288318937</v>
+      </c>
+      <c r="Y3">
+        <v>-0.1622766214554315</v>
+      </c>
+      <c r="Z3">
+        <v>0.6034823632074831</v>
+      </c>
+      <c r="AA3">
+        <v>0.03340559850561078</v>
+      </c>
+      <c r="AB3">
+        <v>0.1973018945581404</v>
+      </c>
+      <c r="AC3">
+        <v>-0.1638962960525296</v>
+      </c>
+      <c r="AD3">
+        <v>0.549</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0.549</v>
+      </c>
+      <c r="AG3">
+        <v>-40.651</v>
+      </c>
+      <c r="AH3">
+        <v>0.0008399003134709913</v>
+      </c>
+      <c r="AI3">
+        <v>0.001349394984379954</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.06637450628542131</v>
+      </c>
+      <c r="AK3">
+        <v>-0.1111749245861468</v>
+      </c>
+      <c r="AL3">
+        <v>3.2</v>
+      </c>
+      <c r="AM3">
+        <v>-18.8</v>
+      </c>
+      <c r="AN3">
+        <v>0.01316546762589928</v>
+      </c>
+      <c r="AO3">
+        <v>7.65625</v>
+      </c>
+      <c r="AP3">
+        <v>-0.9748441247002398</v>
+      </c>
+      <c r="AQ3">
+        <v>-1.303191489361702</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Holcim (Argentina) S.A. (BASE:HARG)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BASE:HARG</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Construction Supplies</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>7.65625</v>
+      </c>
+      <c r="F2">
+        <v>2.00170307757416</v>
+      </c>
+      <c r="G2">
+        <v>0.0131654676258993</v>
+      </c>
+      <c r="H2">
+        <v>3.91875899280576</v>
+      </c>
+      <c r="I2">
+        <v>0.000839900313470991</v>
+      </c>
+      <c r="J2">
+        <v>0.25</v>
+      </c>
+      <c r="K2">
+        <v>653.1</v>
+      </c>
+      <c r="L2">
+        <v>537.7711360846409</v>
+      </c>
+      <c r="M2">
+        <v>612.449</v>
+      </c>
+      <c r="N2">
+        <v>659.983386084641</v>
+      </c>
+      <c r="O2">
+        <v>0.549</v>
+      </c>
+      <c r="P2">
+        <v>163.41225</v>
+      </c>
+      <c r="Q2">
+        <v>0.19730189455814</v>
+      </c>
+      <c r="R2">
+        <v>0.185886015901299</v>
+      </c>
+      <c r="S2">
+        <v>0.118032597311761</v>
+      </c>
+      <c r="T2">
+        <v>0.048685</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.197368528831894</v>
+      </c>
+      <c r="X2">
+        <v>0.231619687868398</v>
+      </c>
+      <c r="Y2">
+        <v>0.715878622640979</v>
+      </c>
+      <c r="Z2">
+        <v>0.870510015992081</v>
+      </c>
+      <c r="AA2">
+        <v>0.549</v>
+      </c>
+      <c r="AB2">
+        <v>0.1815886112488636</v>
+      </c>
+      <c r="AC2">
+        <v>7.65625</v>
+      </c>
+      <c r="AD2">
+        <v>0.549</v>
+      </c>
+      <c r="AE2">
+        <v>3.2</v>
+      </c>
+      <c r="AF2">
+        <v>17.2</v>
+      </c>
+      <c r="AG2">
+        <v>41.7</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>653.1</v>
+      </c>
+      <c r="AK2">
+        <v>0.2215019750791156</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.35</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>32.50000000000001</v>
+      </c>
+      <c r="AR2">
+        <v>3.2</v>
+      </c>
+      <c r="AS2">
+        <v>0.549</v>
+      </c>
+      <c r="AT2">
+        <v>41.2</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1972819352343001</v>
+      </c>
+      <c r="C2">
+        <v>653.7261322479662</v>
+      </c>
+      <c r="D2">
+        <v>612.5261322479662</v>
+      </c>
+      <c r="E2">
+        <v>-0.549</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>41.2</v>
+      </c>
+      <c r="H2">
+        <v>653.1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>41.7</v>
+      </c>
+      <c r="K2">
+        <v>17.2</v>
+      </c>
+      <c r="L2">
+        <v>24.5</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>24.5</v>
+      </c>
+      <c r="O2">
+        <v>8.574999999999999</v>
+      </c>
+      <c r="P2">
+        <v>15.925</v>
+      </c>
+      <c r="Q2">
+        <v>33.125</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1972819352343001</v>
+      </c>
+      <c r="T2">
+        <v>0.7154876843770529</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.35</v>
+      </c>
+      <c r="W2">
+        <v>0.029055</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1966297984609801</v>
+      </c>
+      <c r="C3">
+        <v>649.7205383103926</v>
+      </c>
+      <c r="D3">
+        <v>615.0570283103925</v>
+      </c>
+      <c r="E3">
+        <v>5.98749</v>
+      </c>
+      <c r="F3">
+        <v>6.536490000000001</v>
+      </c>
+      <c r="G3">
+        <v>41.2</v>
+      </c>
+      <c r="H3">
+        <v>653.1</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>41.7</v>
+      </c>
+      <c r="K3">
+        <v>17.2</v>
+      </c>
+      <c r="L3">
+        <v>24.5</v>
+      </c>
+      <c r="M3">
+        <v>0.2921811030000001</v>
+      </c>
+      <c r="N3">
+        <v>24.207818897</v>
+      </c>
+      <c r="O3">
+        <v>8.47273661395</v>
+      </c>
+      <c r="P3">
+        <v>15.73508228305</v>
+      </c>
+      <c r="Q3">
+        <v>32.93508228305</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1983224731929092</v>
+      </c>
+      <c r="T3">
+        <v>0.7201853307896295</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.35</v>
+      </c>
+      <c r="W3">
+        <v>0.029055</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>83.85210319368257</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.19597766168766</v>
+      </c>
+      <c r="C4">
+        <v>645.7359459626633</v>
+      </c>
+      <c r="D4">
+        <v>617.6089259626633</v>
+      </c>
+      <c r="E4">
+        <v>12.52398</v>
+      </c>
+      <c r="F4">
+        <v>13.07298</v>
+      </c>
+      <c r="G4">
+        <v>41.2</v>
+      </c>
+      <c r="H4">
+        <v>653.1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>41.7</v>
+      </c>
+      <c r="K4">
+        <v>17.2</v>
+      </c>
+      <c r="L4">
+        <v>24.5</v>
+      </c>
+      <c r="M4">
+        <v>0.5843622060000001</v>
+      </c>
+      <c r="N4">
+        <v>23.915637794</v>
+      </c>
+      <c r="O4">
+        <v>8.3704732279</v>
+      </c>
+      <c r="P4">
+        <v>15.5451645661</v>
+      </c>
+      <c r="Q4">
+        <v>32.7451645661</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1993842466200612</v>
+      </c>
+      <c r="T4">
+        <v>0.7249788475371567</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.35</v>
+      </c>
+      <c r="W4">
+        <v>0.029055</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>41.92605159684128</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.19532552491434</v>
+      </c>
+      <c r="C5">
+        <v>641.772617703353</v>
+      </c>
+      <c r="D5">
+        <v>620.182087703353</v>
+      </c>
+      <c r="E5">
+        <v>19.06047</v>
+      </c>
+      <c r="F5">
+        <v>19.60947</v>
+      </c>
+      <c r="G5">
+        <v>41.2</v>
+      </c>
+      <c r="H5">
+        <v>653.1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>41.7</v>
+      </c>
+      <c r="K5">
+        <v>17.2</v>
+      </c>
+      <c r="L5">
+        <v>24.5</v>
+      </c>
+      <c r="M5">
+        <v>0.876543309</v>
+      </c>
+      <c r="N5">
+        <v>23.623456691</v>
+      </c>
+      <c r="O5">
+        <v>8.26820984185</v>
+      </c>
+      <c r="P5">
+        <v>15.35524684915</v>
+      </c>
+      <c r="Q5">
+        <v>32.55524684915</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.2004679122828247</v>
+      </c>
+      <c r="T5">
+        <v>0.72987119968154</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.35</v>
+      </c>
+      <c r="W5">
+        <v>0.029055</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>27.95070106456086</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1946733881410199</v>
+      </c>
+      <c r="C6">
+        <v>637.8308204239593</v>
+      </c>
+      <c r="D6">
+        <v>622.7767804239593</v>
+      </c>
+      <c r="E6">
+        <v>25.59696</v>
+      </c>
+      <c r="F6">
+        <v>26.14596</v>
+      </c>
+      <c r="G6">
+        <v>41.2</v>
+      </c>
+      <c r="H6">
+        <v>653.1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>41.7</v>
+      </c>
+      <c r="K6">
+        <v>17.2</v>
+      </c>
+      <c r="L6">
+        <v>24.5</v>
+      </c>
+      <c r="M6">
+        <v>1.168724412</v>
+      </c>
+      <c r="N6">
+        <v>23.331275588</v>
+      </c>
+      <c r="O6">
+        <v>8.1659464558</v>
+      </c>
+      <c r="P6">
+        <v>15.1653291322</v>
+      </c>
+      <c r="Q6">
+        <v>32.3653291322</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.2015741543135624</v>
+      </c>
+      <c r="T6">
+        <v>0.7348654758289315</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.35</v>
+      </c>
+      <c r="W6">
+        <v>0.029055</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>20.96302579842064</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1940212513676998</v>
+      </c>
+      <c r="C7">
+        <v>633.9108255011846</v>
+      </c>
+      <c r="D7">
+        <v>625.3932755011846</v>
+      </c>
+      <c r="E7">
+        <v>32.13345</v>
+      </c>
+      <c r="F7">
+        <v>32.68245</v>
+      </c>
+      <c r="G7">
+        <v>41.2</v>
+      </c>
+      <c r="H7">
+        <v>653.1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>41.7</v>
+      </c>
+      <c r="K7">
+        <v>17.2</v>
+      </c>
+      <c r="L7">
+        <v>24.5</v>
+      </c>
+      <c r="M7">
+        <v>1.460905515</v>
+      </c>
+      <c r="N7">
+        <v>23.039094485</v>
+      </c>
+      <c r="O7">
+        <v>8.063683069749999</v>
+      </c>
+      <c r="P7">
+        <v>14.97541141525</v>
+      </c>
+      <c r="Q7">
+        <v>32.17541141525</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.2027036856502104</v>
+      </c>
+      <c r="T7">
+        <v>0.7399648946320574</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.35</v>
+      </c>
+      <c r="W7">
+        <v>0.029055</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>16.77042063873651</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1933691145943798</v>
+      </c>
+      <c r="C8">
+        <v>630.0129088915522</v>
+      </c>
+      <c r="D8">
+        <v>628.0318488915522</v>
+      </c>
+      <c r="E8">
+        <v>38.66994</v>
+      </c>
+      <c r="F8">
+        <v>39.21894</v>
+      </c>
+      <c r="G8">
+        <v>41.2</v>
+      </c>
+      <c r="H8">
+        <v>653.1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>41.7</v>
+      </c>
+      <c r="K8">
+        <v>17.2</v>
+      </c>
+      <c r="L8">
+        <v>24.5</v>
+      </c>
+      <c r="M8">
+        <v>1.753086618</v>
+      </c>
+      <c r="N8">
+        <v>22.746913382</v>
+      </c>
+      <c r="O8">
+        <v>7.961419683699999</v>
+      </c>
+      <c r="P8">
+        <v>14.7854936983</v>
+      </c>
+      <c r="Q8">
+        <v>31.9854936983</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.2038572495684892</v>
+      </c>
+      <c r="T8">
+        <v>0.7451728117075902</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.35</v>
+      </c>
+      <c r="W8">
+        <v>0.029055</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>13.97535053228043</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1927670278210597</v>
+      </c>
+      <c r="C9">
+        <v>625.932332178914</v>
+      </c>
+      <c r="D9">
+        <v>630.487762178914</v>
+      </c>
+      <c r="E9">
+        <v>45.20643</v>
+      </c>
+      <c r="F9">
+        <v>45.75543</v>
+      </c>
+      <c r="G9">
+        <v>41.2</v>
+      </c>
+      <c r="H9">
+        <v>653.1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>41.7</v>
+      </c>
+      <c r="K9">
+        <v>17.2</v>
+      </c>
+      <c r="L9">
+        <v>24.5</v>
+      </c>
+      <c r="M9">
+        <v>2.095598694</v>
+      </c>
+      <c r="N9">
+        <v>22.404401306</v>
+      </c>
+      <c r="O9">
+        <v>7.8415404571</v>
+      </c>
+      <c r="P9">
+        <v>14.5628608489</v>
+      </c>
+      <c r="Q9">
+        <v>31.7628608489</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.2050356213129675</v>
+      </c>
+      <c r="T9">
+        <v>0.7504927269998011</v>
+      </c>
+      <c r="U9">
+        <v>0.0458</v>
+      </c>
+      <c r="V9">
+        <v>0.35</v>
+      </c>
+      <c r="W9">
+        <v>0.02977</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>11.69116972163946</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1921220410477397</v>
+      </c>
+      <c r="C10">
+        <v>622.04814359994</v>
+      </c>
+      <c r="D10">
+        <v>633.1400635999399</v>
+      </c>
+      <c r="E10">
+        <v>51.74292000000001</v>
+      </c>
+      <c r="F10">
+        <v>52.29192</v>
+      </c>
+      <c r="G10">
+        <v>41.2</v>
+      </c>
+      <c r="H10">
+        <v>653.1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>41.7</v>
+      </c>
+      <c r="K10">
+        <v>17.2</v>
+      </c>
+      <c r="L10">
+        <v>24.5</v>
+      </c>
+      <c r="M10">
+        <v>2.394969936</v>
+      </c>
+      <c r="N10">
+        <v>22.105030064</v>
+      </c>
+      <c r="O10">
+        <v>7.7367605224</v>
+      </c>
+      <c r="P10">
+        <v>14.3682695416</v>
+      </c>
+      <c r="Q10">
+        <v>31.5682695416</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.2062396098344997</v>
+      </c>
+      <c r="T10">
+        <v>0.7559282926244515</v>
+      </c>
+      <c r="U10">
+        <v>0.0458</v>
+      </c>
+      <c r="V10">
+        <v>0.35</v>
+      </c>
+      <c r="W10">
+        <v>0.02977</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>10.22977350643453</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1916057542744197</v>
+      </c>
+      <c r="C11">
+        <v>617.6508521009902</v>
+      </c>
+      <c r="D11">
+        <v>635.2792621009901</v>
+      </c>
+      <c r="E11">
+        <v>58.27941</v>
+      </c>
+      <c r="F11">
+        <v>58.82841</v>
+      </c>
+      <c r="G11">
+        <v>41.2</v>
+      </c>
+      <c r="H11">
+        <v>653.1</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>41.7</v>
+      </c>
+      <c r="K11">
+        <v>17.2</v>
+      </c>
+      <c r="L11">
+        <v>24.5</v>
+      </c>
+      <c r="M11">
+        <v>2.82376368</v>
+      </c>
+      <c r="N11">
+        <v>21.67623632</v>
+      </c>
+      <c r="O11">
+        <v>7.586682712</v>
+      </c>
+      <c r="P11">
+        <v>14.089553608</v>
+      </c>
+      <c r="Q11">
+        <v>31.28955360800001</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.2074700596422194</v>
+      </c>
+      <c r="T11">
+        <v>0.7614833212298634</v>
+      </c>
+      <c r="U11">
+        <v>0.048</v>
+      </c>
+      <c r="V11">
+        <v>0.35</v>
+      </c>
+      <c r="W11">
+        <v>0.0312</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>8.676363455457434</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1909750675010996</v>
+      </c>
+      <c r="C12">
+        <v>613.7472653390236</v>
+      </c>
+      <c r="D12">
+        <v>637.9121653390235</v>
+      </c>
+      <c r="E12">
+        <v>64.8159</v>
+      </c>
+      <c r="F12">
+        <v>65.36490000000001</v>
+      </c>
+      <c r="G12">
+        <v>41.2</v>
+      </c>
+      <c r="H12">
+        <v>653.1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>41.7</v>
+      </c>
+      <c r="K12">
+        <v>17.2</v>
+      </c>
+      <c r="L12">
+        <v>24.5</v>
+      </c>
+      <c r="M12">
+        <v>3.1375152</v>
+      </c>
+      <c r="N12">
+        <v>21.3624848</v>
+      </c>
+      <c r="O12">
+        <v>7.47686968</v>
+      </c>
+      <c r="P12">
+        <v>13.88561512</v>
+      </c>
+      <c r="Q12">
+        <v>31.08561512</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.2087278527789996</v>
+      </c>
+      <c r="T12">
+        <v>0.7671617949153956</v>
+      </c>
+      <c r="U12">
+        <v>0.048</v>
+      </c>
+      <c r="V12">
+        <v>0.35</v>
+      </c>
+      <c r="W12">
+        <v>0.0312</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>7.808727109911691</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1904516307277796</v>
+      </c>
+      <c r="C13">
+        <v>609.4125761629531</v>
+      </c>
+      <c r="D13">
+        <v>640.113966162953</v>
+      </c>
+      <c r="E13">
+        <v>71.35239</v>
+      </c>
+      <c r="F13">
+        <v>71.90139000000001</v>
+      </c>
+      <c r="G13">
+        <v>41.2</v>
+      </c>
+      <c r="H13">
+        <v>653.1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>41.7</v>
+      </c>
+      <c r="K13">
+        <v>17.2</v>
+      </c>
+      <c r="L13">
+        <v>24.5</v>
+      </c>
+      <c r="M13">
+        <v>3.559118805000001</v>
+      </c>
+      <c r="N13">
+        <v>20.940881195</v>
+      </c>
+      <c r="O13">
+        <v>7.329308418249999</v>
+      </c>
+      <c r="P13">
+        <v>13.61157277675</v>
+      </c>
+      <c r="Q13">
+        <v>30.81157277675</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.2100139109300894</v>
+      </c>
+      <c r="T13">
+        <v>0.7729678747511646</v>
+      </c>
+      <c r="U13">
+        <v>0.0495</v>
+      </c>
+      <c r="V13">
+        <v>0.35</v>
+      </c>
+      <c r="W13">
+        <v>0.032175</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>6.883726377883582</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1898306939544595</v>
+      </c>
+      <c r="C14">
+        <v>605.5078048573411</v>
+      </c>
+      <c r="D14">
+        <v>642.745684857341</v>
+      </c>
+      <c r="E14">
+        <v>77.88887999999999</v>
+      </c>
+      <c r="F14">
+        <v>78.43787999999999</v>
+      </c>
+      <c r="G14">
+        <v>41.2</v>
+      </c>
+      <c r="H14">
+        <v>653.1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>41.7</v>
+      </c>
+      <c r="K14">
+        <v>17.2</v>
+      </c>
+      <c r="L14">
+        <v>24.5</v>
+      </c>
+      <c r="M14">
+        <v>3.88267506</v>
+      </c>
+      <c r="N14">
+        <v>20.61732494</v>
+      </c>
+      <c r="O14">
+        <v>7.216063728999999</v>
+      </c>
+      <c r="P14">
+        <v>13.401261211</v>
+      </c>
+      <c r="Q14">
+        <v>30.601261211</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.2113291976755222</v>
+      </c>
+      <c r="T14">
+        <v>0.7789059109468371</v>
+      </c>
+      <c r="U14">
+        <v>0.0495</v>
+      </c>
+      <c r="V14">
+        <v>0.35</v>
+      </c>
+      <c r="W14">
+        <v>0.032175</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>6.310082513059952</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1893280571811395</v>
+      </c>
+      <c r="C15">
+        <v>601.1175434286253</v>
+      </c>
+      <c r="D15">
+        <v>644.8919134286252</v>
+      </c>
+      <c r="E15">
+        <v>84.42537</v>
+      </c>
+      <c r="F15">
+        <v>84.97437000000001</v>
+      </c>
+      <c r="G15">
+        <v>41.2</v>
+      </c>
+      <c r="H15">
+        <v>653.1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>41.7</v>
+      </c>
+      <c r="K15">
+        <v>17.2</v>
+      </c>
+      <c r="L15">
+        <v>24.5</v>
+      </c>
+      <c r="M15">
+        <v>4.325195433</v>
+      </c>
+      <c r="N15">
+        <v>20.174804567</v>
+      </c>
+      <c r="O15">
+        <v>7.061181598449999</v>
+      </c>
+      <c r="P15">
+        <v>13.11362296855</v>
+      </c>
+      <c r="Q15">
+        <v>30.31362296855</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.2126747208978614</v>
+      </c>
+      <c r="T15">
+        <v>0.7849804537217207</v>
+      </c>
+      <c r="U15">
+        <v>0.0509</v>
+      </c>
+      <c r="V15">
+        <v>0.35</v>
+      </c>
+      <c r="W15">
+        <v>0.033085</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>5.664483924372996</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1887162204078194</v>
+      </c>
+      <c r="C16">
+        <v>597.2129806902585</v>
+      </c>
+      <c r="D16">
+        <v>647.5238406902585</v>
+      </c>
+      <c r="E16">
+        <v>90.96186</v>
+      </c>
+      <c r="F16">
+        <v>91.51086000000001</v>
+      </c>
+      <c r="G16">
+        <v>41.2</v>
+      </c>
+      <c r="H16">
+        <v>653.1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>41.7</v>
+      </c>
+      <c r="K16">
+        <v>17.2</v>
+      </c>
+      <c r="L16">
+        <v>24.5</v>
+      </c>
+      <c r="M16">
+        <v>4.657902774</v>
+      </c>
+      <c r="N16">
+        <v>19.842097226</v>
+      </c>
+      <c r="O16">
+        <v>6.944734029099999</v>
+      </c>
+      <c r="P16">
+        <v>12.8973631969</v>
+      </c>
+      <c r="Q16">
+        <v>30.09736319690001</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.2140515353579296</v>
+      </c>
+      <c r="T16">
+        <v>0.7911962649332295</v>
+      </c>
+      <c r="U16">
+        <v>0.0509</v>
+      </c>
+      <c r="V16">
+        <v>0.35</v>
+      </c>
+      <c r="W16">
+        <v>0.033085</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>5.259877929774925</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1881043836344994</v>
+      </c>
+      <c r="C17">
+        <v>593.3299887838282</v>
+      </c>
+      <c r="D17">
+        <v>650.1773387838282</v>
+      </c>
+      <c r="E17">
+        <v>97.49834999999999</v>
+      </c>
+      <c r="F17">
+        <v>98.04734999999999</v>
+      </c>
+      <c r="G17">
+        <v>41.2</v>
+      </c>
+      <c r="H17">
+        <v>653.1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>41.7</v>
+      </c>
+      <c r="K17">
+        <v>17.2</v>
+      </c>
+      <c r="L17">
+        <v>24.5</v>
+      </c>
+      <c r="M17">
+        <v>4.990610115</v>
+      </c>
+      <c r="N17">
+        <v>19.509389885</v>
+      </c>
+      <c r="O17">
+        <v>6.82828645975</v>
+      </c>
+      <c r="P17">
+        <v>12.68110342525</v>
+      </c>
+      <c r="Q17">
+        <v>29.88110342525</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.2154607454523522</v>
+      </c>
+      <c r="T17">
+        <v>0.7975583305261855</v>
+      </c>
+      <c r="U17">
+        <v>0.0509</v>
+      </c>
+      <c r="V17">
+        <v>0.35</v>
+      </c>
+      <c r="W17">
+        <v>0.033085</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>4.909219401123263</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1874925468611793</v>
+      </c>
+      <c r="C18">
+        <v>589.4688339868677</v>
+      </c>
+      <c r="D18">
+        <v>652.8526739868677</v>
+      </c>
+      <c r="E18">
+        <v>104.03484</v>
+      </c>
+      <c r="F18">
+        <v>104.58384</v>
+      </c>
+      <c r="G18">
+        <v>41.2</v>
+      </c>
+      <c r="H18">
+        <v>653.1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>41.7</v>
+      </c>
+      <c r="K18">
+        <v>17.2</v>
+      </c>
+      <c r="L18">
+        <v>24.5</v>
+      </c>
+      <c r="M18">
+        <v>5.323317456000001</v>
+      </c>
+      <c r="N18">
+        <v>19.176682544</v>
+      </c>
+      <c r="O18">
+        <v>6.711838890399999</v>
+      </c>
+      <c r="P18">
+        <v>12.4648436536</v>
+      </c>
+      <c r="Q18">
+        <v>29.6648436536</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.2169035081680706</v>
+      </c>
+      <c r="T18">
+        <v>0.8040718738713547</v>
+      </c>
+      <c r="U18">
+        <v>0.0509</v>
+      </c>
+      <c r="V18">
+        <v>0.35</v>
+      </c>
+      <c r="W18">
+        <v>0.033085</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>4.602393188553059</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1871680100878592</v>
+      </c>
+      <c r="C19">
+        <v>584.360378912615</v>
+      </c>
+      <c r="D19">
+        <v>654.280708912615</v>
+      </c>
+      <c r="E19">
+        <v>110.57133</v>
+      </c>
+      <c r="F19">
+        <v>111.12033</v>
+      </c>
+      <c r="G19">
+        <v>41.2</v>
+      </c>
+      <c r="H19">
+        <v>653.1</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>41.7</v>
+      </c>
+      <c r="K19">
+        <v>17.2</v>
+      </c>
+      <c r="L19">
+        <v>24.5</v>
+      </c>
+      <c r="M19">
+        <v>5.944937655</v>
+      </c>
+      <c r="N19">
+        <v>18.555062345</v>
+      </c>
+      <c r="O19">
+        <v>6.49427182075</v>
+      </c>
+      <c r="P19">
+        <v>12.06079052425</v>
+      </c>
+      <c r="Q19">
+        <v>29.26079052425</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.2183810362504328</v>
+      </c>
+      <c r="T19">
+        <v>0.8107423700682148</v>
+      </c>
+      <c r="U19">
+        <v>0.0535</v>
+      </c>
+      <c r="V19">
+        <v>0.35</v>
+      </c>
+      <c r="W19">
+        <v>0.034775</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>4.12115339500562</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1868889733145392</v>
+      </c>
+      <c r="C20">
+        <v>579.0567178922091</v>
+      </c>
+      <c r="D20">
+        <v>655.5135378922091</v>
+      </c>
+      <c r="E20">
+        <v>117.10782</v>
+      </c>
+      <c r="F20">
+        <v>117.65682</v>
+      </c>
+      <c r="G20">
+        <v>41.2</v>
+      </c>
+      <c r="H20">
+        <v>653.1</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>41.7</v>
+      </c>
+      <c r="K20">
+        <v>17.2</v>
+      </c>
+      <c r="L20">
+        <v>24.5</v>
+      </c>
+      <c r="M20">
+        <v>6.612313284</v>
+      </c>
+      <c r="N20">
+        <v>17.887686716</v>
+      </c>
+      <c r="O20">
+        <v>6.2606903506</v>
+      </c>
+      <c r="P20">
+        <v>11.6269963654</v>
+      </c>
+      <c r="Q20">
+        <v>28.8269963654</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.2198946016030966</v>
+      </c>
+      <c r="T20">
+        <v>0.8175755612942665</v>
+      </c>
+      <c r="U20">
+        <v>0.0562</v>
+      </c>
+      <c r="V20">
+        <v>0.35</v>
+      </c>
+      <c r="W20">
+        <v>0.03653</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>3.705208593077908</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1863115865412192</v>
+      </c>
+      <c r="C21">
+        <v>575.0860253009803</v>
+      </c>
+      <c r="D21">
+        <v>658.0793353009802</v>
+      </c>
+      <c r="E21">
+        <v>123.64431</v>
+      </c>
+      <c r="F21">
+        <v>124.19331</v>
+      </c>
+      <c r="G21">
+        <v>41.2</v>
+      </c>
+      <c r="H21">
+        <v>653.1</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>41.7</v>
+      </c>
+      <c r="K21">
+        <v>17.2</v>
+      </c>
+      <c r="L21">
+        <v>24.5</v>
+      </c>
+      <c r="M21">
+        <v>6.979664022</v>
+      </c>
+      <c r="N21">
+        <v>17.520335978</v>
+      </c>
+      <c r="O21">
+        <v>6.132117592299999</v>
+      </c>
+      <c r="P21">
+        <v>11.3882183857</v>
+      </c>
+      <c r="Q21">
+        <v>28.5882183857</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.2214455389397768</v>
+      </c>
+      <c r="T21">
+        <v>0.824577473291332</v>
+      </c>
+      <c r="U21">
+        <v>0.0562</v>
+      </c>
+      <c r="V21">
+        <v>0.35</v>
+      </c>
+      <c r="W21">
+        <v>0.03653</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>3.51019761449486</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1863451997678992</v>
+      </c>
+      <c r="C22">
+        <v>568.3996139893709</v>
+      </c>
+      <c r="D22">
+        <v>657.9294139893709</v>
+      </c>
+      <c r="E22">
+        <v>130.1808</v>
+      </c>
+      <c r="F22">
+        <v>130.7298</v>
+      </c>
+      <c r="G22">
+        <v>41.2</v>
+      </c>
+      <c r="H22">
+        <v>653.1</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>41.7</v>
+      </c>
+      <c r="K22">
+        <v>17.2</v>
+      </c>
+      <c r="L22">
+        <v>24.5</v>
+      </c>
+      <c r="M22">
+        <v>7.961444820000001</v>
+      </c>
+      <c r="N22">
+        <v>16.53855518</v>
+      </c>
+      <c r="O22">
+        <v>5.788494312999999</v>
+      </c>
+      <c r="P22">
+        <v>10.750060867</v>
+      </c>
+      <c r="Q22">
+        <v>27.950060867</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.2230352497098739</v>
+      </c>
+      <c r="T22">
+        <v>0.8317544330883241</v>
+      </c>
+      <c r="U22">
+        <v>0.0609</v>
+      </c>
+      <c r="V22">
+        <v>0.35</v>
+      </c>
+      <c r="W22">
+        <v>0.039585</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>3.077330880753375</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1870678129945791</v>
+      </c>
+      <c r="C23">
+        <v>558.6565716893928</v>
+      </c>
+      <c r="D23">
+        <v>654.7228616893927</v>
+      </c>
+      <c r="E23">
+        <v>136.71729</v>
+      </c>
+      <c r="F23">
+        <v>137.26629</v>
+      </c>
+      <c r="G23">
+        <v>41.2</v>
+      </c>
+      <c r="H23">
+        <v>653.1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>41.7</v>
+      </c>
+      <c r="K23">
+        <v>17.2</v>
+      </c>
+      <c r="L23">
+        <v>24.5</v>
+      </c>
+      <c r="M23">
+        <v>9.636093557999999</v>
+      </c>
+      <c r="N23">
+        <v>14.863906442</v>
+      </c>
+      <c r="O23">
+        <v>5.2023672547</v>
+      </c>
+      <c r="P23">
+        <v>9.661539187300001</v>
+      </c>
+      <c r="Q23">
+        <v>26.8615391873</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.224665206322252</v>
+      </c>
+      <c r="T23">
+        <v>0.83911308807005</v>
+      </c>
+      <c r="U23">
+        <v>0.0702</v>
+      </c>
+      <c r="V23">
+        <v>0.35</v>
+      </c>
+      <c r="W23">
+        <v>0.04563</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>2.542524089511336</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.187253526221259</v>
+      </c>
+      <c r="C24">
+        <v>551.3010328037218</v>
+      </c>
+      <c r="D24">
+        <v>653.9038128037217</v>
+      </c>
+      <c r="E24">
+        <v>143.25378</v>
+      </c>
+      <c r="F24">
+        <v>143.80278</v>
+      </c>
+      <c r="G24">
+        <v>41.2</v>
+      </c>
+      <c r="H24">
+        <v>653.1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>41.7</v>
+      </c>
+      <c r="K24">
+        <v>17.2</v>
+      </c>
+      <c r="L24">
+        <v>24.5</v>
+      </c>
+      <c r="M24">
+        <v>10.770828222</v>
+      </c>
+      <c r="N24">
+        <v>13.729171778</v>
+      </c>
+      <c r="O24">
+        <v>4.805210122299999</v>
+      </c>
+      <c r="P24">
+        <v>8.923961655700001</v>
+      </c>
+      <c r="Q24">
+        <v>26.1239616557</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.2263369566939218</v>
+      </c>
+      <c r="T24">
+        <v>0.8466604265128459</v>
+      </c>
+      <c r="U24">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V24">
+        <v>0.35</v>
+      </c>
+      <c r="W24">
+        <v>0.048685</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>2.274662588152452</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.186797689447939</v>
+      </c>
+      <c r="C25">
+        <v>546.7785837336985</v>
+      </c>
+      <c r="D25">
+        <v>655.9178537336984</v>
+      </c>
+      <c r="E25">
+        <v>149.79027</v>
+      </c>
+      <c r="F25">
+        <v>150.33927</v>
+      </c>
+      <c r="G25">
+        <v>41.2</v>
+      </c>
+      <c r="H25">
+        <v>653.1</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>41.7</v>
+      </c>
+      <c r="K25">
+        <v>17.2</v>
+      </c>
+      <c r="L25">
+        <v>24.5</v>
+      </c>
+      <c r="M25">
+        <v>11.260411323</v>
+      </c>
+      <c r="N25">
+        <v>13.239588677</v>
+      </c>
+      <c r="O25">
+        <v>4.63385603695</v>
+      </c>
+      <c r="P25">
+        <v>8.60573264005</v>
+      </c>
+      <c r="Q25">
+        <v>25.80573264005</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.2280521291531675</v>
+      </c>
+      <c r="T25">
+        <v>0.8544037997203898</v>
+      </c>
+      <c r="U25">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V25">
+        <v>0.35</v>
+      </c>
+      <c r="W25">
+        <v>0.048685</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>2.17576421475452</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1863418526746189</v>
+      </c>
+      <c r="C26">
+        <v>542.2685795923811</v>
+      </c>
+      <c r="D26">
+        <v>657.9443395923811</v>
+      </c>
+      <c r="E26">
+        <v>156.32676</v>
+      </c>
+      <c r="F26">
+        <v>156.87576</v>
+      </c>
+      <c r="G26">
+        <v>41.2</v>
+      </c>
+      <c r="H26">
+        <v>653.1</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>41.7</v>
+      </c>
+      <c r="K26">
+        <v>17.2</v>
+      </c>
+      <c r="L26">
+        <v>24.5</v>
+      </c>
+      <c r="M26">
+        <v>11.749994424</v>
+      </c>
+      <c r="N26">
+        <v>12.750005576</v>
+      </c>
+      <c r="O26">
+        <v>4.4625019516</v>
+      </c>
+      <c r="P26">
+        <v>8.287503624400001</v>
+      </c>
+      <c r="Q26">
+        <v>25.48750362440001</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.2298124377297617</v>
+      </c>
+      <c r="T26">
+        <v>0.8623509459070795</v>
+      </c>
+      <c r="U26">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V26">
+        <v>0.35</v>
+      </c>
+      <c r="W26">
+        <v>0.048685</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>2.085107372473082</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1858860159012989</v>
+      </c>
+      <c r="C27">
+        <v>537.7711360846409</v>
+      </c>
+      <c r="D27">
+        <v>659.9833860846409</v>
+      </c>
+      <c r="E27">
+        <v>162.86325</v>
+      </c>
+      <c r="F27">
+        <v>163.41225</v>
+      </c>
+      <c r="G27">
+        <v>41.2</v>
+      </c>
+      <c r="H27">
+        <v>653.1</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>41.7</v>
+      </c>
+      <c r="K27">
+        <v>17.2</v>
+      </c>
+      <c r="L27">
+        <v>24.5</v>
+      </c>
+      <c r="M27">
+        <v>12.239577525</v>
+      </c>
+      <c r="N27">
+        <v>12.260422475</v>
+      </c>
+      <c r="O27">
+        <v>4.29114786625</v>
+      </c>
+      <c r="P27">
+        <v>7.96927460875</v>
+      </c>
+      <c r="Q27">
+        <v>25.16927460875</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2316196878683985</v>
+      </c>
+      <c r="T27">
+        <v>0.8705100159920811</v>
+      </c>
+      <c r="U27">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V27">
+        <v>0.35</v>
+      </c>
+      <c r="W27">
+        <v>0.048685</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>2.001703077574159</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1881848791279788</v>
+      </c>
+      <c r="C28">
+        <v>521.0782531126995</v>
+      </c>
+      <c r="D28">
+        <v>649.8269931126995</v>
+      </c>
+      <c r="E28">
+        <v>169.39974</v>
+      </c>
+      <c r="F28">
+        <v>169.94874</v>
+      </c>
+      <c r="G28">
+        <v>41.2</v>
+      </c>
+      <c r="H28">
+        <v>653.1</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>41.7</v>
+      </c>
+      <c r="K28">
+        <v>17.2</v>
+      </c>
+      <c r="L28">
+        <v>24.5</v>
+      </c>
+      <c r="M28">
+        <v>15.499325088</v>
+      </c>
+      <c r="N28">
+        <v>9.000674911999997</v>
+      </c>
+      <c r="O28">
+        <v>3.150236219199999</v>
+      </c>
+      <c r="P28">
+        <v>5.850438692799998</v>
+      </c>
+      <c r="Q28">
+        <v>23.0504386928</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2334757826053768</v>
+      </c>
+      <c r="T28">
+        <v>0.8788896014847852</v>
+      </c>
+      <c r="U28">
+        <v>0.0912</v>
+      </c>
+      <c r="V28">
+        <v>0.35</v>
+      </c>
+      <c r="W28">
+        <v>0.05928000000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>1.580713989860666</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1878349923546588</v>
+      </c>
+      <c r="C29">
+        <v>516.0673502667244</v>
+      </c>
+      <c r="D29">
+        <v>651.3525802667243</v>
+      </c>
+      <c r="E29">
+        <v>175.93623</v>
+      </c>
+      <c r="F29">
+        <v>176.48523</v>
+      </c>
+      <c r="G29">
+        <v>41.2</v>
+      </c>
+      <c r="H29">
+        <v>653.1</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>41.7</v>
+      </c>
+      <c r="K29">
+        <v>17.2</v>
+      </c>
+      <c r="L29">
+        <v>24.5</v>
+      </c>
+      <c r="M29">
+        <v>16.095452976</v>
+      </c>
+      <c r="N29">
+        <v>8.404547023999999</v>
+      </c>
+      <c r="O29">
+        <v>2.9415914584</v>
+      </c>
+      <c r="P29">
+        <v>5.4629555656</v>
+      </c>
+      <c r="Q29">
+        <v>22.6629555656</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2353827292529572</v>
+      </c>
+      <c r="T29">
+        <v>0.8874987646622212</v>
+      </c>
+      <c r="U29">
+        <v>0.0912</v>
+      </c>
+      <c r="V29">
+        <v>0.35</v>
+      </c>
+      <c r="W29">
+        <v>0.05928000000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>1.522169027273234</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.2038709590710011</v>
+      </c>
+      <c r="C30">
+        <v>446.2546282962773</v>
+      </c>
+      <c r="D30">
+        <v>588.0763482962773</v>
+      </c>
+      <c r="E30">
+        <v>182.47272</v>
+      </c>
+      <c r="F30">
+        <v>183.02172</v>
+      </c>
+      <c r="G30">
+        <v>41.2</v>
+      </c>
+      <c r="H30">
+        <v>653.1</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>41.7</v>
+      </c>
+      <c r="K30">
+        <v>17.2</v>
+      </c>
+      <c r="L30">
+        <v>24.5</v>
+      </c>
+      <c r="M30">
+        <v>28.66120135200001</v>
+      </c>
+      <c r="N30">
+        <v>-4.161201352000006</v>
+      </c>
+      <c r="O30">
+        <v>-1.456420473200002</v>
+      </c>
+      <c r="P30">
+        <v>-2.704780878800004</v>
+      </c>
+      <c r="Q30">
+        <v>14.4952191212</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2404744730772954</v>
+      </c>
+      <c r="T30">
+        <v>0.9104861164568024</v>
+      </c>
+      <c r="U30">
+        <v>0.1566</v>
+      </c>
+      <c r="V30">
+        <v>0.2991849467399114</v>
+      </c>
+      <c r="W30">
+        <v>0.1097476373405299</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.8548141335426042</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.2050489590710011</v>
+      </c>
+      <c r="C31">
+        <v>435.5511712237366</v>
+      </c>
+      <c r="D31">
+        <v>583.9093812237365</v>
+      </c>
+      <c r="E31">
+        <v>189.00921</v>
+      </c>
+      <c r="F31">
+        <v>189.55821</v>
+      </c>
+      <c r="G31">
+        <v>41.2</v>
+      </c>
+      <c r="H31">
+        <v>653.1</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>41.7</v>
+      </c>
+      <c r="K31">
+        <v>17.2</v>
+      </c>
+      <c r="L31">
+        <v>24.5</v>
+      </c>
+      <c r="M31">
+        <v>29.684815686</v>
+      </c>
+      <c r="N31">
+        <v>-5.184815686</v>
+      </c>
+      <c r="O31">
+        <v>-1.8146854901</v>
+      </c>
+      <c r="P31">
+        <v>-3.3701301959</v>
+      </c>
+      <c r="Q31">
+        <v>13.8298698041</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2433149586135954</v>
+      </c>
+      <c r="T31">
+        <v>0.9233098645759124</v>
+      </c>
+      <c r="U31">
+        <v>0.1566</v>
+      </c>
+      <c r="V31">
+        <v>0.2888682244385352</v>
+      </c>
+      <c r="W31">
+        <v>0.1113632360529254</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.8253377841101007</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2252060377256629</v>
+      </c>
+      <c r="C32">
+        <v>365.873446808123</v>
+      </c>
+      <c r="D32">
+        <v>520.768146808123</v>
+      </c>
+      <c r="E32">
+        <v>195.5457</v>
+      </c>
+      <c r="F32">
+        <v>196.0947</v>
+      </c>
+      <c r="G32">
+        <v>41.2</v>
+      </c>
+      <c r="H32">
+        <v>653.1</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>41.7</v>
+      </c>
+      <c r="K32">
+        <v>17.2</v>
+      </c>
+      <c r="L32">
+        <v>24.5</v>
+      </c>
+      <c r="M32">
+        <v>40.94457336</v>
+      </c>
+      <c r="N32">
+        <v>-16.44457336</v>
+      </c>
+      <c r="O32">
+        <v>-5.755600675999999</v>
+      </c>
+      <c r="P32">
+        <v>-10.688972684</v>
+      </c>
+      <c r="Q32">
+        <v>6.511027316000003</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2509781418147351</v>
+      </c>
+      <c r="T32">
+        <v>0.9579063199727665</v>
+      </c>
+      <c r="U32">
+        <v>0.2088</v>
+      </c>
+      <c r="V32">
+        <v>0.2094294627179381</v>
+      </c>
+      <c r="W32">
+        <v>0.1650711281844945</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.5983698934798231</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2269060377256629</v>
+      </c>
+      <c r="C33">
+        <v>354.630537703889</v>
+      </c>
+      <c r="D33">
+        <v>516.061727703889</v>
+      </c>
+      <c r="E33">
+        <v>202.08219</v>
+      </c>
+      <c r="F33">
+        <v>202.63119</v>
+      </c>
+      <c r="G33">
+        <v>41.2</v>
+      </c>
+      <c r="H33">
+        <v>653.1</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>41.7</v>
+      </c>
+      <c r="K33">
+        <v>17.2</v>
+      </c>
+      <c r="L33">
+        <v>24.5</v>
+      </c>
+      <c r="M33">
+        <v>42.30939247200001</v>
+      </c>
+      <c r="N33">
+        <v>-17.80939247200001</v>
+      </c>
+      <c r="O33">
+        <v>-6.233287365200002</v>
+      </c>
+      <c r="P33">
+        <v>-11.5761051068</v>
+      </c>
+      <c r="Q33">
+        <v>5.623894893199999</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.254053187348282</v>
+      </c>
+      <c r="T33">
+        <v>0.9717890202622269</v>
+      </c>
+      <c r="U33">
+        <v>0.2088</v>
+      </c>
+      <c r="V33">
+        <v>0.2026736735980045</v>
+      </c>
+      <c r="W33">
+        <v>0.1664817369527367</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.5790676388514415</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2286060377256629</v>
+      </c>
+      <c r="C34">
+        <v>343.4719347953176</v>
+      </c>
+      <c r="D34">
+        <v>511.4396147953175</v>
+      </c>
+      <c r="E34">
+        <v>208.61868</v>
+      </c>
+      <c r="F34">
+        <v>209.16768</v>
+      </c>
+      <c r="G34">
+        <v>41.2</v>
+      </c>
+      <c r="H34">
+        <v>653.1</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>41.7</v>
+      </c>
+      <c r="K34">
+        <v>17.2</v>
+      </c>
+      <c r="L34">
+        <v>24.5</v>
+      </c>
+      <c r="M34">
+        <v>43.67421158400001</v>
+      </c>
+      <c r="N34">
+        <v>-19.17421158400001</v>
+      </c>
+      <c r="O34">
+        <v>-6.710974054400001</v>
+      </c>
+      <c r="P34">
+        <v>-12.4632375296</v>
+      </c>
+      <c r="Q34">
+        <v>4.736762470399999</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2572186753975214</v>
+      </c>
+      <c r="T34">
+        <v>0.9860800352660831</v>
+      </c>
+      <c r="U34">
+        <v>0.2088</v>
+      </c>
+      <c r="V34">
+        <v>0.1963401212980669</v>
+      </c>
+      <c r="W34">
+        <v>0.1678041826729637</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.560971775137334</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2303060377256629</v>
+      </c>
+      <c r="C35">
+        <v>332.3953929229189</v>
+      </c>
+      <c r="D35">
+        <v>506.8995629229188</v>
+      </c>
+      <c r="E35">
+        <v>215.15517</v>
+      </c>
+      <c r="F35">
+        <v>215.70417</v>
+      </c>
+      <c r="G35">
+        <v>41.2</v>
+      </c>
+      <c r="H35">
+        <v>653.1</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>41.7</v>
+      </c>
+      <c r="K35">
+        <v>17.2</v>
+      </c>
+      <c r="L35">
+        <v>24.5</v>
+      </c>
+      <c r="M35">
+        <v>45.039030696</v>
+      </c>
+      <c r="N35">
+        <v>-20.539030696</v>
+      </c>
+      <c r="O35">
+        <v>-7.188660743600001</v>
+      </c>
+      <c r="P35">
+        <v>-13.3503699524</v>
+      </c>
+      <c r="Q35">
+        <v>3.849630047599998</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2604786556273352</v>
+      </c>
+      <c r="T35">
+        <v>1.000797647732741</v>
+      </c>
+      <c r="U35">
+        <v>0.2088</v>
+      </c>
+      <c r="V35">
+        <v>0.1903904206526709</v>
+      </c>
+      <c r="W35">
+        <v>0.1690464801677223</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.5439726304362027</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2320060377256629</v>
+      </c>
+      <c r="C36">
+        <v>321.3987459469109</v>
+      </c>
+      <c r="D36">
+        <v>502.439405946911</v>
+      </c>
+      <c r="E36">
+        <v>221.69166</v>
+      </c>
+      <c r="F36">
+        <v>222.24066</v>
+      </c>
+      <c r="G36">
+        <v>41.2</v>
+      </c>
+      <c r="H36">
+        <v>653.1</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>41.7</v>
+      </c>
+      <c r="K36">
+        <v>17.2</v>
+      </c>
+      <c r="L36">
+        <v>24.5</v>
+      </c>
+      <c r="M36">
+        <v>46.403849808</v>
+      </c>
+      <c r="N36">
+        <v>-21.903849808</v>
+      </c>
+      <c r="O36">
+        <v>-7.666347432800001</v>
+      </c>
+      <c r="P36">
+        <v>-14.2375023752</v>
+      </c>
+      <c r="Q36">
+        <v>2.962497624800001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2638374231368402</v>
+      </c>
+      <c r="T36">
+        <v>1.015961248455965</v>
+      </c>
+      <c r="U36">
+        <v>0.2088</v>
+      </c>
+      <c r="V36">
+        <v>0.1847907023981806</v>
+      </c>
+      <c r="W36">
+        <v>0.1702157013392599</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.5279734354233732</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2337060377256629</v>
+      </c>
+      <c r="C37">
+        <v>310.4799033011095</v>
+      </c>
+      <c r="D37">
+        <v>498.0570533011095</v>
+      </c>
+      <c r="E37">
+        <v>228.22815</v>
+      </c>
+      <c r="F37">
+        <v>228.77715</v>
+      </c>
+      <c r="G37">
+        <v>41.2</v>
+      </c>
+      <c r="H37">
+        <v>653.1</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>41.7</v>
+      </c>
+      <c r="K37">
+        <v>17.2</v>
+      </c>
+      <c r="L37">
+        <v>24.5</v>
+      </c>
+      <c r="M37">
+        <v>47.76866892000001</v>
+      </c>
+      <c r="N37">
+        <v>-23.26866892000001</v>
+      </c>
+      <c r="O37">
+        <v>-8.144034122000003</v>
+      </c>
+      <c r="P37">
+        <v>-15.12463479800001</v>
+      </c>
+      <c r="Q37">
+        <v>2.075365201999995</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2672995373389455</v>
+      </c>
+      <c r="T37">
+        <v>1.031591421509133</v>
+      </c>
+      <c r="U37">
+        <v>0.2088</v>
+      </c>
+      <c r="V37">
+        <v>0.1795109680439469</v>
+      </c>
+      <c r="W37">
+        <v>0.1713181098724239</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.5128884801255624</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2474569467663646</v>
+      </c>
+      <c r="C38">
+        <v>271.120459916806</v>
+      </c>
+      <c r="D38">
+        <v>465.234099916806</v>
+      </c>
+      <c r="E38">
+        <v>234.76464</v>
+      </c>
+      <c r="F38">
+        <v>235.31364</v>
+      </c>
+      <c r="G38">
+        <v>41.2</v>
+      </c>
+      <c r="H38">
+        <v>653.1</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>41.7</v>
+      </c>
+      <c r="K38">
+        <v>17.2</v>
+      </c>
+      <c r="L38">
+        <v>24.5</v>
+      </c>
+      <c r="M38">
+        <v>56.192897232</v>
+      </c>
+      <c r="N38">
+        <v>-31.692897232</v>
+      </c>
+      <c r="O38">
+        <v>-11.0925140312</v>
+      </c>
+      <c r="P38">
+        <v>-20.6003832008</v>
+      </c>
+      <c r="Q38">
+        <v>-3.4003832008</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2728243879859629</v>
+      </c>
+      <c r="T38">
+        <v>1.056534091411034</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.152599357256789</v>
+      </c>
+      <c r="W38">
+        <v>0.2023592734870788</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.4359981635908259</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2494569467663646</v>
+      </c>
+      <c r="C39">
+        <v>260.1669866930552</v>
+      </c>
+      <c r="D39">
+        <v>460.8171166930551</v>
+      </c>
+      <c r="E39">
+        <v>241.30113</v>
+      </c>
+      <c r="F39">
+        <v>241.85013</v>
+      </c>
+      <c r="G39">
+        <v>41.2</v>
+      </c>
+      <c r="H39">
+        <v>653.1</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>41.7</v>
+      </c>
+      <c r="K39">
+        <v>17.2</v>
+      </c>
+      <c r="L39">
+        <v>24.5</v>
+      </c>
+      <c r="M39">
+        <v>57.753811044</v>
+      </c>
+      <c r="N39">
+        <v>-33.253811044</v>
+      </c>
+      <c r="O39">
+        <v>-11.6388338654</v>
+      </c>
+      <c r="P39">
+        <v>-21.6149771786</v>
+      </c>
+      <c r="Q39">
+        <v>-4.414977178599997</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2765390608111369</v>
+      </c>
+      <c r="T39">
+        <v>1.073304473814384</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.1484750503039028</v>
+      </c>
+      <c r="W39">
+        <v>0.203344157987428</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.4242144294397224</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2514569467663647</v>
+      </c>
+      <c r="C40">
+        <v>249.2965953209138</v>
+      </c>
+      <c r="D40">
+        <v>456.4832153209138</v>
+      </c>
+      <c r="E40">
+        <v>247.83762</v>
+      </c>
+      <c r="F40">
+        <v>248.38662</v>
+      </c>
+      <c r="G40">
+        <v>41.2</v>
+      </c>
+      <c r="H40">
+        <v>653.1</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>41.7</v>
+      </c>
+      <c r="K40">
+        <v>17.2</v>
+      </c>
+      <c r="L40">
+        <v>24.5</v>
+      </c>
+      <c r="M40">
+        <v>59.314724856</v>
+      </c>
+      <c r="N40">
+        <v>-34.814724856</v>
+      </c>
+      <c r="O40">
+        <v>-12.1851536996</v>
+      </c>
+      <c r="P40">
+        <v>-22.6295711564</v>
+      </c>
+      <c r="Q40">
+        <v>-5.429571156399994</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2803735617919617</v>
+      </c>
+      <c r="T40">
+        <v>1.090615836295261</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.1445678121380106</v>
+      </c>
+      <c r="W40">
+        <v>0.2042772064614431</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.4130508918228877</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2534569467663646</v>
+      </c>
+      <c r="C41">
+        <v>238.5069635316779</v>
+      </c>
+      <c r="D41">
+        <v>452.2300735316779</v>
+      </c>
+      <c r="E41">
+        <v>254.37411</v>
+      </c>
+      <c r="F41">
+        <v>254.92311</v>
+      </c>
+      <c r="G41">
+        <v>41.2</v>
+      </c>
+      <c r="H41">
+        <v>653.1</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>41.7</v>
+      </c>
+      <c r="K41">
+        <v>17.2</v>
+      </c>
+      <c r="L41">
+        <v>24.5</v>
+      </c>
+      <c r="M41">
+        <v>60.87563866800001</v>
+      </c>
+      <c r="N41">
+        <v>-36.37563866800001</v>
+      </c>
+      <c r="O41">
+        <v>-12.7314735338</v>
+      </c>
+      <c r="P41">
+        <v>-23.6441651342</v>
+      </c>
+      <c r="Q41">
+        <v>-6.444165134200002</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2843337841164201</v>
+      </c>
+      <c r="T41">
+        <v>1.108494784431249</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.1408609451601129</v>
+      </c>
+      <c r="W41">
+        <v>0.205162406295765</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.4024598433146084</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2554569467663646</v>
+      </c>
+      <c r="C42">
+        <v>227.7958548057956</v>
+      </c>
+      <c r="D42">
+        <v>448.0554548057956</v>
+      </c>
+      <c r="E42">
+        <v>260.9106</v>
+      </c>
+      <c r="F42">
+        <v>261.4596</v>
+      </c>
+      <c r="G42">
+        <v>41.2</v>
+      </c>
+      <c r="H42">
+        <v>653.1</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>41.7</v>
+      </c>
+      <c r="K42">
+        <v>17.2</v>
+      </c>
+      <c r="L42">
+        <v>24.5</v>
+      </c>
+      <c r="M42">
+        <v>62.43655248000001</v>
+      </c>
+      <c r="N42">
+        <v>-37.93655248000001</v>
+      </c>
+      <c r="O42">
+        <v>-13.277793368</v>
+      </c>
+      <c r="P42">
+        <v>-24.65875911200001</v>
+      </c>
+      <c r="Q42">
+        <v>-7.458759112000003</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2884260138516938</v>
+      </c>
+      <c r="T42">
+        <v>1.126969697505103</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.1373394215311101</v>
+      </c>
+      <c r="W42">
+        <v>0.2060033461383709</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.3923983472317432</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2574569467663647</v>
+      </c>
+      <c r="C43">
+        <v>217.1611144512385</v>
+      </c>
+      <c r="D43">
+        <v>443.9572044512386</v>
+      </c>
+      <c r="E43">
+        <v>267.4470900000001</v>
+      </c>
+      <c r="F43">
+        <v>267.99609</v>
+      </c>
+      <c r="G43">
+        <v>41.2</v>
+      </c>
+      <c r="H43">
+        <v>653.1</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>41.7</v>
+      </c>
+      <c r="K43">
+        <v>17.2</v>
+      </c>
+      <c r="L43">
+        <v>24.5</v>
+      </c>
+      <c r="M43">
+        <v>63.99746629200001</v>
+      </c>
+      <c r="N43">
+        <v>-39.49746629200001</v>
+      </c>
+      <c r="O43">
+        <v>-13.8241132022</v>
+      </c>
+      <c r="P43">
+        <v>-25.67335308980001</v>
+      </c>
+      <c r="Q43">
+        <v>-8.473353089800007</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2926569632390106</v>
+      </c>
+      <c r="T43">
+        <v>1.146070878818749</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.1339896795425464</v>
+      </c>
+      <c r="W43">
+        <v>0.2068032645252399</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.382827655835847</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2594569467663647</v>
+      </c>
+      <c r="C44">
+        <v>206.6006658951428</v>
+      </c>
+      <c r="D44">
+        <v>439.9332458951428</v>
+      </c>
+      <c r="E44">
+        <v>273.98358</v>
+      </c>
+      <c r="F44">
+        <v>274.53258</v>
+      </c>
+      <c r="G44">
+        <v>41.2</v>
+      </c>
+      <c r="H44">
+        <v>653.1</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>41.7</v>
+      </c>
+      <c r="K44">
+        <v>17.2</v>
+      </c>
+      <c r="L44">
+        <v>24.5</v>
+      </c>
+      <c r="M44">
+        <v>65.55838010400001</v>
+      </c>
+      <c r="N44">
+        <v>-41.05838010400001</v>
+      </c>
+      <c r="O44">
+        <v>-14.3704330364</v>
+      </c>
+      <c r="P44">
+        <v>-26.68794706760001</v>
+      </c>
+      <c r="Q44">
+        <v>-9.487947067600004</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2970338074327867</v>
+      </c>
+      <c r="T44">
+        <v>1.165830721557003</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.1307994490772477</v>
+      </c>
+      <c r="W44">
+        <v>0.2075650915603532</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.3737127116492792</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2614569467663647</v>
+      </c>
+      <c r="C45">
+        <v>196.1125071753093</v>
+      </c>
+      <c r="D45">
+        <v>435.9815771753093</v>
+      </c>
+      <c r="E45">
+        <v>280.52007</v>
+      </c>
+      <c r="F45">
+        <v>281.06907</v>
+      </c>
+      <c r="G45">
+        <v>41.2</v>
+      </c>
+      <c r="H45">
+        <v>653.1</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>41.7</v>
+      </c>
+      <c r="K45">
+        <v>17.2</v>
+      </c>
+      <c r="L45">
+        <v>24.5</v>
+      </c>
+      <c r="M45">
+        <v>67.119293916</v>
+      </c>
+      <c r="N45">
+        <v>-42.619293916</v>
+      </c>
+      <c r="O45">
+        <v>-14.9167528706</v>
+      </c>
+      <c r="P45">
+        <v>-27.7025410454</v>
+      </c>
+      <c r="Q45">
+        <v>-10.5025410454</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.3015642251070461</v>
+      </c>
+      <c r="T45">
+        <v>1.186283892110634</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.1277576014242885</v>
+      </c>
+      <c r="W45">
+        <v>0.2082914847798799</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.36502171835511</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2634569467663647</v>
+      </c>
+      <c r="C46">
+        <v>185.6947076191109</v>
+      </c>
+      <c r="D46">
+        <v>432.100267619111</v>
+      </c>
+      <c r="E46">
+        <v>287.05656</v>
+      </c>
+      <c r="F46">
+        <v>287.60556</v>
+      </c>
+      <c r="G46">
+        <v>41.2</v>
+      </c>
+      <c r="H46">
+        <v>653.1</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>41.7</v>
+      </c>
+      <c r="K46">
+        <v>17.2</v>
+      </c>
+      <c r="L46">
+        <v>24.5</v>
+      </c>
+      <c r="M46">
+        <v>68.68020772800001</v>
+      </c>
+      <c r="N46">
+        <v>-44.18020772800001</v>
+      </c>
+      <c r="O46">
+        <v>-15.4630727048</v>
+      </c>
+      <c r="P46">
+        <v>-28.71713502320001</v>
+      </c>
+      <c r="Q46">
+        <v>-11.51713502320001</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.3062564434125291</v>
+      </c>
+      <c r="T46">
+        <v>1.207467533041182</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.1248540195737364</v>
+      </c>
+      <c r="W46">
+        <v>0.2089848601257918</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.3567257702106756</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
         <v>0.45</v>
       </c>
-      <c r="E3">
-        <v>0.5760000000000001</v>
-      </c>
-      <c r="G3">
-        <v>0.4607276436586195</v>
-      </c>
-      <c r="H3">
-        <v>0.4607276436586195</v>
-      </c>
-      <c r="I3">
-        <v>0.1904114246854811</v>
-      </c>
-      <c r="J3">
-        <v>0.1671117930893517</v>
-      </c>
-      <c r="K3">
-        <v>61.6</v>
-      </c>
-      <c r="L3">
-        <v>0.2094525671540292</v>
-      </c>
-      <c r="M3">
-        <v>13.4</v>
-      </c>
-      <c r="N3">
-        <v>0.02289033139733516</v>
-      </c>
-      <c r="O3">
-        <v>0.2175324675324675</v>
-      </c>
-      <c r="P3">
-        <v>13.4</v>
-      </c>
-      <c r="Q3">
-        <v>0.02289033139733516</v>
-      </c>
-      <c r="R3">
-        <v>0.2175324675324675</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>53.1</v>
-      </c>
-      <c r="V3">
-        <v>0.09070720874615648</v>
-      </c>
-      <c r="W3">
-        <v>0.2030323005932762</v>
-      </c>
-      <c r="X3">
-        <v>0.289789045337049</v>
-      </c>
-      <c r="Y3">
-        <v>-0.08675674474377273</v>
-      </c>
-      <c r="Z3">
-        <v>1.242973669751913</v>
-      </c>
-      <c r="AA3">
-        <v>0.2077155587150939</v>
-      </c>
-      <c r="AB3">
-        <v>0.2895365083373939</v>
-      </c>
-      <c r="AC3">
-        <v>-0.08182094962229999</v>
-      </c>
-      <c r="AD3">
-        <v>0.905</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0.905</v>
-      </c>
-      <c r="AG3">
-        <v>-52.195</v>
-      </c>
-      <c r="AH3">
-        <v>0.001543565209234102</v>
-      </c>
-      <c r="AI3">
-        <v>0.002155762794630841</v>
-      </c>
-      <c r="AJ3">
-        <v>-0.09788917958383737</v>
-      </c>
-      <c r="AK3">
-        <v>-0.142335119510233</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>-10.3</v>
-      </c>
-      <c r="AN3">
-        <v>0.01193931398416887</v>
-      </c>
-      <c r="AP3">
-        <v>-0.6885883905013193</v>
-      </c>
-      <c r="AQ3">
-        <v>-5.436893203883495</v>
+      <c r="B47">
+        <v>0.2654569467663647</v>
+      </c>
+      <c r="C47">
+        <v>175.34540469823</v>
+      </c>
+      <c r="D47">
+        <v>428.28745469823</v>
+      </c>
+      <c r="E47">
+        <v>293.59305</v>
+      </c>
+      <c r="F47">
+        <v>294.14205</v>
+      </c>
+      <c r="G47">
+        <v>41.2</v>
+      </c>
+      <c r="H47">
+        <v>653.1</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>41.7</v>
+      </c>
+      <c r="K47">
+        <v>17.2</v>
+      </c>
+      <c r="L47">
+        <v>24.5</v>
+      </c>
+      <c r="M47">
+        <v>70.24112153999999</v>
+      </c>
+      <c r="N47">
+        <v>-45.74112153999999</v>
+      </c>
+      <c r="O47">
+        <v>-16.009392539</v>
+      </c>
+      <c r="P47">
+        <v>-29.731729001</v>
+      </c>
+      <c r="Q47">
+        <v>-12.531729001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.3111192878382114</v>
+      </c>
+      <c r="T47">
+        <v>1.229421488187385</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.1220794858054312</v>
+      </c>
+      <c r="W47">
+        <v>0.209647418789663</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.3487985308726607</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2674569467663647</v>
+      </c>
+      <c r="C48">
+        <v>165.0628010484589</v>
+      </c>
+      <c r="D48">
+        <v>424.5413410484589</v>
+      </c>
+      <c r="E48">
+        <v>300.12954</v>
+      </c>
+      <c r="F48">
+        <v>300.67854</v>
+      </c>
+      <c r="G48">
+        <v>41.2</v>
+      </c>
+      <c r="H48">
+        <v>653.1</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>41.7</v>
+      </c>
+      <c r="K48">
+        <v>17.2</v>
+      </c>
+      <c r="L48">
+        <v>24.5</v>
+      </c>
+      <c r="M48">
+        <v>71.802035352</v>
+      </c>
+      <c r="N48">
+        <v>-47.302035352</v>
+      </c>
+      <c r="O48">
+        <v>-16.5557123732</v>
+      </c>
+      <c r="P48">
+        <v>-30.7463229788</v>
+      </c>
+      <c r="Q48">
+        <v>-13.5463229788</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.3161622376129931</v>
+      </c>
+      <c r="T48">
+        <v>1.252188552783448</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.1194255839400958</v>
+      </c>
+      <c r="W48">
+        <v>0.2102811705551051</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.3412159541145593</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2694569467663647</v>
+      </c>
+      <c r="C49">
+        <v>154.845161644548</v>
+      </c>
+      <c r="D49">
+        <v>420.860191644548</v>
+      </c>
+      <c r="E49">
+        <v>306.66603</v>
+      </c>
+      <c r="F49">
+        <v>307.21503</v>
+      </c>
+      <c r="G49">
+        <v>41.2</v>
+      </c>
+      <c r="H49">
+        <v>653.1</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>41.7</v>
+      </c>
+      <c r="K49">
+        <v>17.2</v>
+      </c>
+      <c r="L49">
+        <v>24.5</v>
+      </c>
+      <c r="M49">
+        <v>73.362949164</v>
+      </c>
+      <c r="N49">
+        <v>-48.862949164</v>
+      </c>
+      <c r="O49">
+        <v>-17.1020322074</v>
+      </c>
+      <c r="P49">
+        <v>-31.7609169566</v>
+      </c>
+      <c r="Q49">
+        <v>-14.5609169566</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.321395487379276</v>
+      </c>
+      <c r="T49">
+        <v>1.275814751892569</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.1168846140690299</v>
+      </c>
+      <c r="W49">
+        <v>0.2108879541603157</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.3339560401972282</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2714569467663646</v>
+      </c>
+      <c r="C50">
+        <v>144.6908111207686</v>
+      </c>
+      <c r="D50">
+        <v>417.2423311207686</v>
+      </c>
+      <c r="E50">
+        <v>313.20252</v>
+      </c>
+      <c r="F50">
+        <v>313.75152</v>
+      </c>
+      <c r="G50">
+        <v>41.2</v>
+      </c>
+      <c r="H50">
+        <v>653.1</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>41.7</v>
+      </c>
+      <c r="K50">
+        <v>17.2</v>
+      </c>
+      <c r="L50">
+        <v>24.5</v>
+      </c>
+      <c r="M50">
+        <v>74.923862976</v>
+      </c>
+      <c r="N50">
+        <v>-50.423862976</v>
+      </c>
+      <c r="O50">
+        <v>-17.6483520416</v>
+      </c>
+      <c r="P50">
+        <v>-32.7755109344</v>
+      </c>
+      <c r="Q50">
+        <v>-15.5755109344</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.3268300159827236</v>
+      </c>
+      <c r="T50">
+        <v>1.300349650967426</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.1144495179425918</v>
+      </c>
+      <c r="W50">
+        <v>0.2114694551153091</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.3269986226931194</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2734569467663646</v>
+      </c>
+      <c r="C51">
+        <v>134.5981312284984</v>
+      </c>
+      <c r="D51">
+        <v>413.6861412284984</v>
+      </c>
+      <c r="E51">
+        <v>319.73901</v>
+      </c>
+      <c r="F51">
+        <v>320.28801</v>
+      </c>
+      <c r="G51">
+        <v>41.2</v>
+      </c>
+      <c r="H51">
+        <v>653.1</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>41.7</v>
+      </c>
+      <c r="K51">
+        <v>17.2</v>
+      </c>
+      <c r="L51">
+        <v>24.5</v>
+      </c>
+      <c r="M51">
+        <v>76.484776788</v>
+      </c>
+      <c r="N51">
+        <v>-51.984776788</v>
+      </c>
+      <c r="O51">
+        <v>-18.1946718758</v>
+      </c>
+      <c r="P51">
+        <v>-33.79010491220001</v>
+      </c>
+      <c r="Q51">
+        <v>-16.5901049122</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.3324776633549338</v>
+      </c>
+      <c r="T51">
+        <v>1.32584670294718</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.1121138134947838</v>
+      </c>
+      <c r="W51">
+        <v>0.2120272213374456</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.3203251814136679</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2754569467663646</v>
+      </c>
+      <c r="C52">
+        <v>124.5655584227238</v>
+      </c>
+      <c r="D52">
+        <v>410.1900584227238</v>
+      </c>
+      <c r="E52">
+        <v>326.2755</v>
+      </c>
+      <c r="F52">
+        <v>326.8245</v>
+      </c>
+      <c r="G52">
+        <v>41.2</v>
+      </c>
+      <c r="H52">
+        <v>653.1</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>41.7</v>
+      </c>
+      <c r="K52">
+        <v>17.2</v>
+      </c>
+      <c r="L52">
+        <v>24.5</v>
+      </c>
+      <c r="M52">
+        <v>78.0456906</v>
+      </c>
+      <c r="N52">
+        <v>-53.5456906</v>
+      </c>
+      <c r="O52">
+        <v>-18.74099171</v>
+      </c>
+      <c r="P52">
+        <v>-34.80469889</v>
+      </c>
+      <c r="Q52">
+        <v>-17.60469888999999</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.3383512166220325</v>
+      </c>
+      <c r="T52">
+        <v>1.352363637006123</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.1098715372248881</v>
+      </c>
+      <c r="W52">
+        <v>0.2125626769106967</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.3139186777853946</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2774569467663647</v>
+      </c>
+      <c r="C53">
+        <v>114.5915815698957</v>
+      </c>
+      <c r="D53">
+        <v>406.7525715698957</v>
+      </c>
+      <c r="E53">
+        <v>332.81199</v>
+      </c>
+      <c r="F53">
+        <v>333.36099</v>
+      </c>
+      <c r="G53">
+        <v>41.2</v>
+      </c>
+      <c r="H53">
+        <v>653.1</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>41.7</v>
+      </c>
+      <c r="K53">
+        <v>17.2</v>
+      </c>
+      <c r="L53">
+        <v>24.5</v>
+      </c>
+      <c r="M53">
+        <v>79.60660441200001</v>
+      </c>
+      <c r="N53">
+        <v>-55.10660441200001</v>
+      </c>
+      <c r="O53">
+        <v>-19.2873115442</v>
+      </c>
+      <c r="P53">
+        <v>-35.81929286780001</v>
+      </c>
+      <c r="Q53">
+        <v>-18.61929286780001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.344464506757176</v>
+      </c>
+      <c r="T53">
+        <v>1.379962894904208</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.1077171933577334</v>
+      </c>
+      <c r="W53">
+        <v>0.2130771342261733</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.3077634095935241</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2794569467663646</v>
+      </c>
+      <c r="C54">
+        <v>104.6747397700802</v>
+      </c>
+      <c r="D54">
+        <v>403.3722197700802</v>
+      </c>
+      <c r="E54">
+        <v>339.3484800000001</v>
+      </c>
+      <c r="F54">
+        <v>339.89748</v>
+      </c>
+      <c r="G54">
+        <v>41.2</v>
+      </c>
+      <c r="H54">
+        <v>653.1</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>41.7</v>
+      </c>
+      <c r="K54">
+        <v>17.2</v>
+      </c>
+      <c r="L54">
+        <v>24.5</v>
+      </c>
+      <c r="M54">
+        <v>81.16751822400001</v>
+      </c>
+      <c r="N54">
+        <v>-56.66751822400001</v>
+      </c>
+      <c r="O54">
+        <v>-19.8336313784</v>
+      </c>
+      <c r="P54">
+        <v>-36.83388684560001</v>
+      </c>
+      <c r="Q54">
+        <v>-19.6338868456</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.3508325173146172</v>
+      </c>
+      <c r="T54">
+        <v>1.408712121881379</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.1056457088700847</v>
+      </c>
+      <c r="W54">
+        <v>0.2135718047218238</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.3018448824859563</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2814569467663647</v>
+      </c>
+      <c r="C55">
+        <v>94.81362028680832</v>
+      </c>
+      <c r="D55">
+        <v>400.0475902868084</v>
+      </c>
+      <c r="E55">
+        <v>345.8849700000001</v>
+      </c>
+      <c r="F55">
+        <v>346.43397</v>
+      </c>
+      <c r="G55">
+        <v>41.2</v>
+      </c>
+      <c r="H55">
+        <v>653.1</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>41.7</v>
+      </c>
+      <c r="K55">
+        <v>17.2</v>
+      </c>
+      <c r="L55">
+        <v>24.5</v>
+      </c>
+      <c r="M55">
+        <v>82.72843203600002</v>
+      </c>
+      <c r="N55">
+        <v>-58.22843203600002</v>
+      </c>
+      <c r="O55">
+        <v>-20.37995121260001</v>
+      </c>
+      <c r="P55">
+        <v>-37.84848082340001</v>
+      </c>
+      <c r="Q55">
+        <v>-20.64848082340001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.3574715070447155</v>
+      </c>
+      <c r="T55">
+        <v>1.438684720219281</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.103652393608385</v>
+      </c>
+      <c r="W55">
+        <v>0.2140478084063177</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.2961496960239571</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2834569467663646</v>
+      </c>
+      <c r="C56">
+        <v>85.00685657846503</v>
+      </c>
+      <c r="D56">
+        <v>396.777316578465</v>
+      </c>
+      <c r="E56">
+        <v>352.42146</v>
+      </c>
+      <c r="F56">
+        <v>352.97046</v>
+      </c>
+      <c r="G56">
+        <v>41.2</v>
+      </c>
+      <c r="H56">
+        <v>653.1</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>41.7</v>
+      </c>
+      <c r="K56">
+        <v>17.2</v>
+      </c>
+      <c r="L56">
+        <v>24.5</v>
+      </c>
+      <c r="M56">
+        <v>84.28934584800001</v>
+      </c>
+      <c r="N56">
+        <v>-59.78934584800001</v>
+      </c>
+      <c r="O56">
+        <v>-20.9262710468</v>
+      </c>
+      <c r="P56">
+        <v>-38.86307480120001</v>
+      </c>
+      <c r="Q56">
+        <v>-21.6630748012</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.3643991485022093</v>
+      </c>
+      <c r="T56">
+        <v>1.469960475006656</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.1017329048378594</v>
+      </c>
+      <c r="W56">
+        <v>0.2145061823247192</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.2906654423938838</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2854569467663647</v>
+      </c>
+      <c r="C57">
+        <v>75.25312642544958</v>
+      </c>
+      <c r="D57">
+        <v>393.5600764254496</v>
+      </c>
+      <c r="E57">
+        <v>358.95795</v>
+      </c>
+      <c r="F57">
+        <v>359.50695</v>
+      </c>
+      <c r="G57">
+        <v>41.2</v>
+      </c>
+      <c r="H57">
+        <v>653.1</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>41.7</v>
+      </c>
+      <c r="K57">
+        <v>17.2</v>
+      </c>
+      <c r="L57">
+        <v>24.5</v>
+      </c>
+      <c r="M57">
+        <v>85.85025966000001</v>
+      </c>
+      <c r="N57">
+        <v>-61.35025966000001</v>
+      </c>
+      <c r="O57">
+        <v>-21.472590881</v>
+      </c>
+      <c r="P57">
+        <v>-39.877668779</v>
+      </c>
+      <c r="Q57">
+        <v>-22.677668779</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.3716346851355918</v>
+      </c>
+      <c r="T57">
+        <v>1.502626263340137</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.09988321565898918</v>
+      </c>
+      <c r="W57">
+        <v>0.2149478881006334</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.2853806161685405</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2874569467663646</v>
+      </c>
+      <c r="C58">
+        <v>65.5511501477207</v>
+      </c>
+      <c r="D58">
+        <v>390.3945901477207</v>
+      </c>
+      <c r="E58">
+        <v>365.4944400000001</v>
+      </c>
+      <c r="F58">
+        <v>366.04344</v>
+      </c>
+      <c r="G58">
+        <v>41.2</v>
+      </c>
+      <c r="H58">
+        <v>653.1</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>41.7</v>
+      </c>
+      <c r="K58">
+        <v>17.2</v>
+      </c>
+      <c r="L58">
+        <v>24.5</v>
+      </c>
+      <c r="M58">
+        <v>87.41117347200002</v>
+      </c>
+      <c r="N58">
+        <v>-62.91117347200002</v>
+      </c>
+      <c r="O58">
+        <v>-22.0189107152</v>
+      </c>
+      <c r="P58">
+        <v>-40.89226275680001</v>
+      </c>
+      <c r="Q58">
+        <v>-23.69226275680001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.3791991097977643</v>
+      </c>
+      <c r="T58">
+        <v>1.536776860234231</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.09809958680793578</v>
+      </c>
+      <c r="W58">
+        <v>0.2153738186702649</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.2802845337369594</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2894569467663646</v>
+      </c>
+      <c r="C59">
+        <v>55.89968890767278</v>
+      </c>
+      <c r="D59">
+        <v>387.2796189076728</v>
+      </c>
+      <c r="E59">
+        <v>372.0309300000001</v>
+      </c>
+      <c r="F59">
+        <v>372.57993</v>
+      </c>
+      <c r="G59">
+        <v>41.2</v>
+      </c>
+      <c r="H59">
+        <v>653.1</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>41.7</v>
+      </c>
+      <c r="K59">
+        <v>17.2</v>
+      </c>
+      <c r="L59">
+        <v>24.5</v>
+      </c>
+      <c r="M59">
+        <v>88.97208728400001</v>
+      </c>
+      <c r="N59">
+        <v>-64.47208728400001</v>
+      </c>
+      <c r="O59">
+        <v>-22.5652305494</v>
+      </c>
+      <c r="P59">
+        <v>-41.90685673460001</v>
+      </c>
+      <c r="Q59">
+        <v>-24.70685673460001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.3871153681651541</v>
+      </c>
+      <c r="T59">
+        <v>1.572515856983865</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.09637854142534043</v>
+      </c>
+      <c r="W59">
+        <v>0.2157848043076287</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.2753672612152583</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2914569467663646</v>
+      </c>
+      <c r="C60">
+        <v>46.29754309361931</v>
+      </c>
+      <c r="D60">
+        <v>384.2139630936193</v>
+      </c>
+      <c r="E60">
+        <v>378.56742</v>
+      </c>
+      <c r="F60">
+        <v>379.1164199999999</v>
+      </c>
+      <c r="G60">
+        <v>41.2</v>
+      </c>
+      <c r="H60">
+        <v>653.1</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>41.7</v>
+      </c>
+      <c r="K60">
+        <v>17.2</v>
+      </c>
+      <c r="L60">
+        <v>24.5</v>
+      </c>
+      <c r="M60">
+        <v>90.53300109599999</v>
+      </c>
+      <c r="N60">
+        <v>-66.03300109599999</v>
+      </c>
+      <c r="O60">
+        <v>-23.1115503836</v>
+      </c>
+      <c r="P60">
+        <v>-42.9214507124</v>
+      </c>
+      <c r="Q60">
+        <v>-25.72145071239999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.3954085912167054</v>
+      </c>
+      <c r="T60">
+        <v>1.609956710721575</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.09471684243524837</v>
+      </c>
+      <c r="W60">
+        <v>0.2161816180264627</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.2706195498149954</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2934569467663646</v>
+      </c>
+      <c r="C61">
+        <v>36.74355077944824</v>
+      </c>
+      <c r="D61">
+        <v>381.1964607794482</v>
+      </c>
+      <c r="E61">
+        <v>385.10391</v>
+      </c>
+      <c r="F61">
+        <v>385.65291</v>
+      </c>
+      <c r="G61">
+        <v>41.2</v>
+      </c>
+      <c r="H61">
+        <v>653.1</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>41.7</v>
+      </c>
+      <c r="K61">
+        <v>17.2</v>
+      </c>
+      <c r="L61">
+        <v>24.5</v>
+      </c>
+      <c r="M61">
+        <v>92.093914908</v>
+      </c>
+      <c r="N61">
+        <v>-67.593914908</v>
+      </c>
+      <c r="O61">
+        <v>-23.6578702178</v>
+      </c>
+      <c r="P61">
+        <v>-43.93604469020001</v>
+      </c>
+      <c r="Q61">
+        <v>-26.7360446902</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.404106361734186</v>
+      </c>
+      <c r="T61">
+        <v>1.649223947568443</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.09311147222448143</v>
+      </c>
+      <c r="W61">
+        <v>0.2165649804327938</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.2660327777842327</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2954569467663646</v>
+      </c>
+      <c r="C62">
+        <v>27.23658625629849</v>
+      </c>
+      <c r="D62">
+        <v>378.2259862562985</v>
+      </c>
+      <c r="E62">
+        <v>391.6404</v>
+      </c>
+      <c r="F62">
+        <v>392.1894</v>
+      </c>
+      <c r="G62">
+        <v>41.2</v>
+      </c>
+      <c r="H62">
+        <v>653.1</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>41.7</v>
+      </c>
+      <c r="K62">
+        <v>17.2</v>
+      </c>
+      <c r="L62">
+        <v>24.5</v>
+      </c>
+      <c r="M62">
+        <v>93.65482872</v>
+      </c>
+      <c r="N62">
+        <v>-69.15482872</v>
+      </c>
+      <c r="O62">
+        <v>-24.204190052</v>
+      </c>
+      <c r="P62">
+        <v>-44.950638668</v>
+      </c>
+      <c r="Q62">
+        <v>-27.75063866799999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.4132390207775406</v>
+      </c>
+      <c r="T62">
+        <v>1.690454546257654</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.09155961435407342</v>
+      </c>
+      <c r="W62">
+        <v>0.2169355640922473</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2615988981544956</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2974569467663646</v>
+      </c>
+      <c r="C63">
+        <v>17.77555863235494</v>
+      </c>
+      <c r="D63">
+        <v>375.3014486323549</v>
+      </c>
+      <c r="E63">
+        <v>398.17689</v>
+      </c>
+      <c r="F63">
+        <v>398.72589</v>
+      </c>
+      <c r="G63">
+        <v>41.2</v>
+      </c>
+      <c r="H63">
+        <v>653.1</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>41.7</v>
+      </c>
+      <c r="K63">
+        <v>17.2</v>
+      </c>
+      <c r="L63">
+        <v>24.5</v>
+      </c>
+      <c r="M63">
+        <v>95.21574253200001</v>
+      </c>
+      <c r="N63">
+        <v>-70.71574253200001</v>
+      </c>
+      <c r="O63">
+        <v>-24.7505098862</v>
+      </c>
+      <c r="P63">
+        <v>-45.96523264580001</v>
+      </c>
+      <c r="Q63">
+        <v>-28.7652326458</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.4228400213102981</v>
+      </c>
+      <c r="T63">
+        <v>1.733799534623235</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.09005863706958041</v>
+      </c>
+      <c r="W63">
+        <v>0.2172939974677842</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2573103916273726</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2994569467663646</v>
+      </c>
+      <c r="C64">
+        <v>8.359410497106751</v>
+      </c>
+      <c r="D64">
+        <v>372.4217904971068</v>
+      </c>
+      <c r="E64">
+        <v>404.71338</v>
+      </c>
+      <c r="F64">
+        <v>405.26238</v>
+      </c>
+      <c r="G64">
+        <v>41.2</v>
+      </c>
+      <c r="H64">
+        <v>653.1</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>41.7</v>
+      </c>
+      <c r="K64">
+        <v>17.2</v>
+      </c>
+      <c r="L64">
+        <v>24.5</v>
+      </c>
+      <c r="M64">
+        <v>96.776656344</v>
+      </c>
+      <c r="N64">
+        <v>-72.276656344</v>
+      </c>
+      <c r="O64">
+        <v>-25.2968297204</v>
+      </c>
+      <c r="P64">
+        <v>-46.9798266236</v>
+      </c>
+      <c r="Q64">
+        <v>-29.7798266236</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.4329463376605691</v>
+      </c>
+      <c r="T64">
+        <v>1.779425838165952</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.08860607840716782</v>
+      </c>
+      <c r="W64">
+        <v>0.2176408684763683</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2531602240204796</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.3014569467663646</v>
+      </c>
+      <c r="C65">
+        <v>-1.01288335336892</v>
+      </c>
+      <c r="D65">
+        <v>369.5859866466311</v>
+      </c>
+      <c r="E65">
+        <v>411.24987</v>
+      </c>
+      <c r="F65">
+        <v>411.79887</v>
+      </c>
+      <c r="G65">
+        <v>41.2</v>
+      </c>
+      <c r="H65">
+        <v>653.1</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>41.7</v>
+      </c>
+      <c r="K65">
+        <v>17.2</v>
+      </c>
+      <c r="L65">
+        <v>24.5</v>
+      </c>
+      <c r="M65">
+        <v>98.33757015600001</v>
+      </c>
+      <c r="N65">
+        <v>-73.83757015600001</v>
+      </c>
+      <c r="O65">
+        <v>-25.8431495546</v>
+      </c>
+      <c r="P65">
+        <v>-47.99442060140001</v>
+      </c>
+      <c r="Q65">
+        <v>-30.79442060140001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.443598941381125</v>
+      </c>
+      <c r="T65">
+        <v>1.827518428386653</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.08719963271816515</v>
+      </c>
+      <c r="W65">
+        <v>0.2179767277069022</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2491418077661861</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.3034569467663646</v>
+      </c>
+      <c r="C66">
+        <v>-10.34231713332485</v>
+      </c>
+      <c r="D66">
+        <v>366.7930428666752</v>
+      </c>
+      <c r="E66">
+        <v>417.7863600000001</v>
+      </c>
+      <c r="F66">
+        <v>418.33536</v>
+      </c>
+      <c r="G66">
+        <v>41.2</v>
+      </c>
+      <c r="H66">
+        <v>653.1</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>41.7</v>
+      </c>
+      <c r="K66">
+        <v>17.2</v>
+      </c>
+      <c r="L66">
+        <v>24.5</v>
+      </c>
+      <c r="M66">
+        <v>99.89848396800001</v>
+      </c>
+      <c r="N66">
+        <v>-75.39848396800001</v>
+      </c>
+      <c r="O66">
+        <v>-26.3894693888</v>
+      </c>
+      <c r="P66">
+        <v>-49.00901457920001</v>
+      </c>
+      <c r="Q66">
+        <v>-31.8090145792</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.4548433564194896</v>
+      </c>
+      <c r="T66">
+        <v>1.878282829175171</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.08583713845694382</v>
+      </c>
+      <c r="W66">
+        <v>0.2183020913364818</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2452489670198396</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.3054569467663646</v>
+      </c>
+      <c r="C67">
+        <v>-19.62985522949958</v>
+      </c>
+      <c r="D67">
+        <v>364.0419947705004</v>
+      </c>
+      <c r="E67">
+        <v>424.32285</v>
+      </c>
+      <c r="F67">
+        <v>424.87185</v>
+      </c>
+      <c r="G67">
+        <v>41.2</v>
+      </c>
+      <c r="H67">
+        <v>653.1</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>41.7</v>
+      </c>
+      <c r="K67">
+        <v>17.2</v>
+      </c>
+      <c r="L67">
+        <v>24.5</v>
+      </c>
+      <c r="M67">
+        <v>101.45939778</v>
+      </c>
+      <c r="N67">
+        <v>-76.95939778</v>
+      </c>
+      <c r="O67">
+        <v>-26.935789223</v>
+      </c>
+      <c r="P67">
+        <v>-50.023608557</v>
+      </c>
+      <c r="Q67">
+        <v>-32.823608557</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.4667303094600465</v>
+      </c>
+      <c r="T67">
+        <v>1.931948052865891</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.08451656709606777</v>
+      </c>
+      <c r="W67">
+        <v>0.218617443777459</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2414759059887651</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.3074569467663646</v>
+      </c>
+      <c r="C68">
+        <v>-28.87643331136161</v>
+      </c>
+      <c r="D68">
+        <v>361.3319066886384</v>
+      </c>
+      <c r="E68">
+        <v>430.85934</v>
+      </c>
+      <c r="F68">
+        <v>431.40834</v>
+      </c>
+      <c r="G68">
+        <v>41.2</v>
+      </c>
+      <c r="H68">
+        <v>653.1</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>41.7</v>
+      </c>
+      <c r="K68">
+        <v>17.2</v>
+      </c>
+      <c r="L68">
+        <v>24.5</v>
+      </c>
+      <c r="M68">
+        <v>103.020311592</v>
+      </c>
+      <c r="N68">
+        <v>-78.52031159200001</v>
+      </c>
+      <c r="O68">
+        <v>-27.4821090572</v>
+      </c>
+      <c r="P68">
+        <v>-51.03820253480001</v>
+      </c>
+      <c r="Q68">
+        <v>-33.8382025348</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.4793164950324008</v>
+      </c>
+      <c r="T68">
+        <v>1.98877005442077</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.08323601304915765</v>
+      </c>
+      <c r="W68">
+        <v>0.2189232400838612</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2378171801404504</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.3094569467663646</v>
+      </c>
+      <c r="C69">
+        <v>-38.08295939213178</v>
+      </c>
+      <c r="D69">
+        <v>358.6618706078683</v>
+      </c>
+      <c r="E69">
+        <v>437.39583</v>
+      </c>
+      <c r="F69">
+        <v>437.94483</v>
+      </c>
+      <c r="G69">
+        <v>41.2</v>
+      </c>
+      <c r="H69">
+        <v>653.1</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>41.7</v>
+      </c>
+      <c r="K69">
+        <v>17.2</v>
+      </c>
+      <c r="L69">
+        <v>24.5</v>
+      </c>
+      <c r="M69">
+        <v>104.581225404</v>
+      </c>
+      <c r="N69">
+        <v>-80.08122540400001</v>
+      </c>
+      <c r="O69">
+        <v>-28.0284288914</v>
+      </c>
+      <c r="P69">
+        <v>-52.05279651260001</v>
+      </c>
+      <c r="Q69">
+        <v>-34.85279651260001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.4926654797303523</v>
+      </c>
+      <c r="T69">
+        <v>2.049035813645641</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.08199368449618515</v>
+      </c>
+      <c r="W69">
+        <v>0.219219908142311</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.2342676699891004</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.3114569467663646</v>
+      </c>
+      <c r="C70">
+        <v>-47.25031484310597</v>
+      </c>
+      <c r="D70">
+        <v>356.0310051568941</v>
+      </c>
+      <c r="E70">
+        <v>443.9323200000001</v>
+      </c>
+      <c r="F70">
+        <v>444.48132</v>
+      </c>
+      <c r="G70">
+        <v>41.2</v>
+      </c>
+      <c r="H70">
+        <v>653.1</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>41.7</v>
+      </c>
+      <c r="K70">
+        <v>17.2</v>
+      </c>
+      <c r="L70">
+        <v>24.5</v>
+      </c>
+      <c r="M70">
+        <v>106.142139216</v>
+      </c>
+      <c r="N70">
+        <v>-81.64213921600002</v>
+      </c>
+      <c r="O70">
+        <v>-28.5747487256</v>
+      </c>
+      <c r="P70">
+        <v>-53.06739049040002</v>
+      </c>
+      <c r="Q70">
+        <v>-35.86739049040001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.5068487759719259</v>
+      </c>
+      <c r="T70">
+        <v>2.113068182822068</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.08078789501830007</v>
+      </c>
+      <c r="W70">
+        <v>0.2195078506696299</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.230822557195143</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.3134569467663646</v>
+      </c>
+      <c r="C71">
+        <v>-56.37935536366319</v>
+      </c>
+      <c r="D71">
+        <v>353.4384546363369</v>
+      </c>
+      <c r="E71">
+        <v>450.4688100000001</v>
+      </c>
+      <c r="F71">
+        <v>451.0178100000001</v>
+      </c>
+      <c r="G71">
+        <v>41.2</v>
+      </c>
+      <c r="H71">
+        <v>653.1</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>41.7</v>
+      </c>
+      <c r="K71">
+        <v>17.2</v>
+      </c>
+      <c r="L71">
+        <v>24.5</v>
+      </c>
+      <c r="M71">
+        <v>107.703053028</v>
+      </c>
+      <c r="N71">
+        <v>-83.20305302800001</v>
+      </c>
+      <c r="O71">
+        <v>-29.1210685598</v>
+      </c>
+      <c r="P71">
+        <v>-54.08198446820001</v>
+      </c>
+      <c r="Q71">
+        <v>-36.88198446820001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.5219471235839235</v>
+      </c>
+      <c r="T71">
+        <v>2.181231672590522</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.07961705596006384</v>
+      </c>
+      <c r="W71">
+        <v>0.2197874470367367</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2274773027430396</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.3154569467663646</v>
+      </c>
+      <c r="C72">
+        <v>-65.47091190919855</v>
+      </c>
+      <c r="D72">
+        <v>350.8833880908015</v>
+      </c>
+      <c r="E72">
+        <v>457.0053000000001</v>
+      </c>
+      <c r="F72">
+        <v>457.5543000000001</v>
+      </c>
+      <c r="G72">
+        <v>41.2</v>
+      </c>
+      <c r="H72">
+        <v>653.1</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>41.7</v>
+      </c>
+      <c r="K72">
+        <v>17.2</v>
+      </c>
+      <c r="L72">
+        <v>24.5</v>
+      </c>
+      <c r="M72">
+        <v>109.26396684</v>
+      </c>
+      <c r="N72">
+        <v>-84.76396684000002</v>
+      </c>
+      <c r="O72">
+        <v>-29.66738839400001</v>
+      </c>
+      <c r="P72">
+        <v>-55.09657844600002</v>
+      </c>
+      <c r="Q72">
+        <v>-37.89657844600001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.5380520277033876</v>
+      </c>
+      <c r="T72">
+        <v>2.253939395010206</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.07847966944634863</v>
+      </c>
+      <c r="W72">
+        <v>0.2200590549362119</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.2242276269895676</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.3174569467663647</v>
+      </c>
+      <c r="C73">
+        <v>-74.52579157909605</v>
+      </c>
+      <c r="D73">
+        <v>348.3649984209039</v>
+      </c>
+      <c r="E73">
+        <v>463.54179</v>
+      </c>
+      <c r="F73">
+        <v>464.09079</v>
+      </c>
+      <c r="G73">
+        <v>41.2</v>
+      </c>
+      <c r="H73">
+        <v>653.1</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>41.7</v>
+      </c>
+      <c r="K73">
+        <v>17.2</v>
+      </c>
+      <c r="L73">
+        <v>24.5</v>
+      </c>
+      <c r="M73">
+        <v>110.824880652</v>
+      </c>
+      <c r="N73">
+        <v>-86.324880652</v>
+      </c>
+      <c r="O73">
+        <v>-30.2137082282</v>
+      </c>
+      <c r="P73">
+        <v>-56.11117242380001</v>
+      </c>
+      <c r="Q73">
+        <v>-38.9111724238</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.5552676148655733</v>
+      </c>
+      <c r="T73">
+        <v>2.331661443114006</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.07737432198935781</v>
+      </c>
+      <c r="W73">
+        <v>0.2203230119089414</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.2210694913981652</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.3194569467663646</v>
+      </c>
+      <c r="C74">
+        <v>-83.54477846673512</v>
+      </c>
+      <c r="D74">
+        <v>345.8825015332649</v>
+      </c>
+      <c r="E74">
+        <v>470.07828</v>
+      </c>
+      <c r="F74">
+        <v>470.62728</v>
+      </c>
+      <c r="G74">
+        <v>41.2</v>
+      </c>
+      <c r="H74">
+        <v>653.1</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>41.7</v>
+      </c>
+      <c r="K74">
+        <v>17.2</v>
+      </c>
+      <c r="L74">
+        <v>24.5</v>
+      </c>
+      <c r="M74">
+        <v>112.385794464</v>
+      </c>
+      <c r="N74">
+        <v>-87.885794464</v>
+      </c>
+      <c r="O74">
+        <v>-30.7600280624</v>
+      </c>
+      <c r="P74">
+        <v>-57.1257664016</v>
+      </c>
+      <c r="Q74">
+        <v>-39.9257664016</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.5737128868250581</v>
+      </c>
+      <c r="T74">
+        <v>2.414935066082363</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.07629967862839451</v>
+      </c>
+      <c r="W74">
+        <v>0.2205796367435394</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.2179990817954129</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.3214569467663646</v>
+      </c>
+      <c r="C75">
+        <v>-92.52863447341008</v>
+      </c>
+      <c r="D75">
+        <v>343.4351355265899</v>
+      </c>
+      <c r="E75">
+        <v>476.61477</v>
+      </c>
+      <c r="F75">
+        <v>477.16377</v>
+      </c>
+      <c r="G75">
+        <v>41.2</v>
+      </c>
+      <c r="H75">
+        <v>653.1</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>41.7</v>
+      </c>
+      <c r="K75">
+        <v>17.2</v>
+      </c>
+      <c r="L75">
+        <v>24.5</v>
+      </c>
+      <c r="M75">
+        <v>113.946708276</v>
+      </c>
+      <c r="N75">
+        <v>-89.44670827600001</v>
+      </c>
+      <c r="O75">
+        <v>-31.3063478966</v>
+      </c>
+      <c r="P75">
+        <v>-58.14036037940001</v>
+      </c>
+      <c r="Q75">
+        <v>-40.9403603794</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.5935244752259861</v>
+      </c>
+      <c r="T75">
+        <v>2.504377105566895</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.07525447755129322</v>
+      </c>
+      <c r="W75">
+        <v>0.2208292307607512</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.2150127930036949</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.3234569467663646</v>
+      </c>
+      <c r="C76">
+        <v>-101.4781000879379</v>
+      </c>
+      <c r="D76">
+        <v>341.0221599120621</v>
+      </c>
+      <c r="E76">
+        <v>483.15126</v>
+      </c>
+      <c r="F76">
+        <v>483.70026</v>
+      </c>
+      <c r="G76">
+        <v>41.2</v>
+      </c>
+      <c r="H76">
+        <v>653.1</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>41.7</v>
+      </c>
+      <c r="K76">
+        <v>17.2</v>
+      </c>
+      <c r="L76">
+        <v>24.5</v>
+      </c>
+      <c r="M76">
+        <v>115.507622088</v>
+      </c>
+      <c r="N76">
+        <v>-91.00762208800001</v>
+      </c>
+      <c r="O76">
+        <v>-31.8526677308</v>
+      </c>
+      <c r="P76">
+        <v>-59.1549543572</v>
+      </c>
+      <c r="Q76">
+        <v>-41.9549543572</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.6148600319654471</v>
+      </c>
+      <c r="T76">
+        <v>2.600699301934853</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.07423752515195142</v>
+      </c>
+      <c r="W76">
+        <v>0.221072078993714</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2121072147198612</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.3254569467663646</v>
+      </c>
+      <c r="C77">
+        <v>-110.3938951336308</v>
+      </c>
+      <c r="D77">
+        <v>338.6428548663692</v>
+      </c>
+      <c r="E77">
+        <v>489.6877500000001</v>
+      </c>
+      <c r="F77">
+        <v>490.23675</v>
+      </c>
+      <c r="G77">
+        <v>41.2</v>
+      </c>
+      <c r="H77">
+        <v>653.1</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>41.7</v>
+      </c>
+      <c r="K77">
+        <v>17.2</v>
+      </c>
+      <c r="L77">
+        <v>24.5</v>
+      </c>
+      <c r="M77">
+        <v>117.0685359</v>
+      </c>
+      <c r="N77">
+        <v>-92.56853590000001</v>
+      </c>
+      <c r="O77">
+        <v>-32.39898756500001</v>
+      </c>
+      <c r="P77">
+        <v>-60.16954833500001</v>
+      </c>
+      <c r="Q77">
+        <v>-42.96954833500001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.637902433244065</v>
+      </c>
+      <c r="T77">
+        <v>2.704727274012247</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.07324769148325873</v>
+      </c>
+      <c r="W77">
+        <v>0.2213084512737978</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2092791185235964</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.3274569467663646</v>
+      </c>
+      <c r="C78">
+        <v>-119.2767194842152</v>
+      </c>
+      <c r="D78">
+        <v>336.2965205157848</v>
+      </c>
+      <c r="E78">
+        <v>496.22424</v>
+      </c>
+      <c r="F78">
+        <v>496.77324</v>
+      </c>
+      <c r="G78">
+        <v>41.2</v>
+      </c>
+      <c r="H78">
+        <v>653.1</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>41.7</v>
+      </c>
+      <c r="K78">
+        <v>17.2</v>
+      </c>
+      <c r="L78">
+        <v>24.5</v>
+      </c>
+      <c r="M78">
+        <v>118.629449712</v>
+      </c>
+      <c r="N78">
+        <v>-94.129449712</v>
+      </c>
+      <c r="O78">
+        <v>-32.9453073992</v>
+      </c>
+      <c r="P78">
+        <v>-61.1841423128</v>
+      </c>
+      <c r="Q78">
+        <v>-43.9841423128</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.6628650346292344</v>
+      </c>
+      <c r="T78">
+        <v>2.817424243762757</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.07228390606900532</v>
+      </c>
+      <c r="W78">
+        <v>0.2215386032307215</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2065254459114438</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.3294569467663646</v>
+      </c>
+      <c r="C79">
+        <v>-128.1272537501939</v>
+      </c>
+      <c r="D79">
+        <v>333.9824762498062</v>
+      </c>
+      <c r="E79">
+        <v>502.76073</v>
+      </c>
+      <c r="F79">
+        <v>503.30973</v>
+      </c>
+      <c r="G79">
+        <v>41.2</v>
+      </c>
+      <c r="H79">
+        <v>653.1</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>41.7</v>
+      </c>
+      <c r="K79">
+        <v>17.2</v>
+      </c>
+      <c r="L79">
+        <v>24.5</v>
+      </c>
+      <c r="M79">
+        <v>120.190363524</v>
+      </c>
+      <c r="N79">
+        <v>-95.69036352400001</v>
+      </c>
+      <c r="O79">
+        <v>-33.4916272334</v>
+      </c>
+      <c r="P79">
+        <v>-62.1987362906</v>
+      </c>
+      <c r="Q79">
+        <v>-44.9987362906</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.6899982970044185</v>
+      </c>
+      <c r="T79">
+        <v>2.939920950013312</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.07134515404213512</v>
+      </c>
+      <c r="W79">
+        <v>0.2217627772147381</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2038432972632432</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.3314569467663647</v>
+      </c>
+      <c r="C80">
+        <v>-136.9461599370643</v>
+      </c>
+      <c r="D80">
+        <v>331.7000600629357</v>
+      </c>
+      <c r="E80">
+        <v>509.29722</v>
+      </c>
+      <c r="F80">
+        <v>509.84622</v>
+      </c>
+      <c r="G80">
+        <v>41.2</v>
+      </c>
+      <c r="H80">
+        <v>653.1</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>41.7</v>
+      </c>
+      <c r="K80">
+        <v>17.2</v>
+      </c>
+      <c r="L80">
+        <v>24.5</v>
+      </c>
+      <c r="M80">
+        <v>121.751277336</v>
+      </c>
+      <c r="N80">
+        <v>-97.25127733600002</v>
+      </c>
+      <c r="O80">
+        <v>-34.0379470676</v>
+      </c>
+      <c r="P80">
+        <v>-63.21333026840001</v>
+      </c>
+      <c r="Q80">
+        <v>-46.01333026840001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.7195982195955286</v>
+      </c>
+      <c r="T80">
+        <v>3.073553720468463</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.07043047258005647</v>
+      </c>
+      <c r="W80">
+        <v>0.2219812031478825</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2012299216573042</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.3334569467663646</v>
+      </c>
+      <c r="C81">
+        <v>-145.734082076731</v>
+      </c>
+      <c r="D81">
+        <v>329.448627923269</v>
+      </c>
+      <c r="E81">
+        <v>515.83371</v>
+      </c>
+      <c r="F81">
+        <v>516.38271</v>
+      </c>
+      <c r="G81">
+        <v>41.2</v>
+      </c>
+      <c r="H81">
+        <v>653.1</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>41.7</v>
+      </c>
+      <c r="K81">
+        <v>17.2</v>
+      </c>
+      <c r="L81">
+        <v>24.5</v>
+      </c>
+      <c r="M81">
+        <v>123.312191148</v>
+      </c>
+      <c r="N81">
+        <v>-98.812191148</v>
+      </c>
+      <c r="O81">
+        <v>-34.5842669018</v>
+      </c>
+      <c r="P81">
+        <v>-64.22792424619999</v>
+      </c>
+      <c r="Q81">
+        <v>-47.02792424619999</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.7520171824334108</v>
+      </c>
+      <c r="T81">
+        <v>3.219913421443152</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.06953894761068867</v>
+      </c>
+      <c r="W81">
+        <v>0.2221940993105675</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1986827074591105</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.3354569467663646</v>
+      </c>
+      <c r="C82">
+        <v>-154.4916468333773</v>
+      </c>
+      <c r="D82">
+        <v>327.2275531666227</v>
+      </c>
+      <c r="E82">
+        <v>522.3702000000001</v>
+      </c>
+      <c r="F82">
+        <v>522.9192</v>
+      </c>
+      <c r="G82">
+        <v>41.2</v>
+      </c>
+      <c r="H82">
+        <v>653.1</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>41.7</v>
+      </c>
+      <c r="K82">
+        <v>17.2</v>
+      </c>
+      <c r="L82">
+        <v>24.5</v>
+      </c>
+      <c r="M82">
+        <v>124.87310496</v>
+      </c>
+      <c r="N82">
+        <v>-100.37310496</v>
+      </c>
+      <c r="O82">
+        <v>-35.13058673600001</v>
+      </c>
+      <c r="P82">
+        <v>-65.24251822400001</v>
+      </c>
+      <c r="Q82">
+        <v>-48.04251822400001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.7876780415550815</v>
+      </c>
+      <c r="T82">
+        <v>3.38090909251531</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.06866971076555504</v>
+      </c>
+      <c r="W82">
+        <v>0.2224016730691855</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1961991736158716</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.3374569467663646</v>
+      </c>
+      <c r="C83">
+        <v>-163.2194640849922</v>
+      </c>
+      <c r="D83">
+        <v>325.0362259150078</v>
+      </c>
+      <c r="E83">
+        <v>528.90669</v>
+      </c>
+      <c r="F83">
+        <v>529.45569</v>
+      </c>
+      <c r="G83">
+        <v>41.2</v>
+      </c>
+      <c r="H83">
+        <v>653.1</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>41.7</v>
+      </c>
+      <c r="K83">
+        <v>17.2</v>
+      </c>
+      <c r="L83">
+        <v>24.5</v>
+      </c>
+      <c r="M83">
+        <v>126.434018772</v>
+      </c>
+      <c r="N83">
+        <v>-101.934018772</v>
+      </c>
+      <c r="O83">
+        <v>-35.6769065702</v>
+      </c>
+      <c r="P83">
+        <v>-66.2571122018</v>
+      </c>
+      <c r="Q83">
+        <v>-49.0571122018</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.8270926753211383</v>
+      </c>
+      <c r="T83">
+        <v>3.558851676331904</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.0678219365585729</v>
+      </c>
+      <c r="W83">
+        <v>0.2226041215498128</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1937769615959226</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3394569467663646</v>
+      </c>
+      <c r="C84">
+        <v>-171.9181274816881</v>
+      </c>
+      <c r="D84">
+        <v>322.874052518312</v>
+      </c>
+      <c r="E84">
+        <v>535.4431800000001</v>
+      </c>
+      <c r="F84">
+        <v>535.9921800000001</v>
+      </c>
+      <c r="G84">
+        <v>41.2</v>
+      </c>
+      <c r="H84">
+        <v>653.1</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>41.7</v>
+      </c>
+      <c r="K84">
+        <v>17.2</v>
+      </c>
+      <c r="L84">
+        <v>24.5</v>
+      </c>
+      <c r="M84">
+        <v>127.994932584</v>
+      </c>
+      <c r="N84">
+        <v>-103.494932584</v>
+      </c>
+      <c r="O84">
+        <v>-36.22322640440001</v>
+      </c>
+      <c r="P84">
+        <v>-67.27170617960002</v>
+      </c>
+      <c r="Q84">
+        <v>-50.07170617960001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.8708867128389794</v>
+      </c>
+      <c r="T84">
+        <v>3.756565658350344</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.06699483977127321</v>
+      </c>
+      <c r="W84">
+        <v>0.22280163226262</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1914138279179235</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3414569467663647</v>
+      </c>
+      <c r="C85">
+        <v>-180.5882149818807</v>
+      </c>
+      <c r="D85">
+        <v>320.7404550181193</v>
+      </c>
+      <c r="E85">
+        <v>541.9796700000001</v>
+      </c>
+      <c r="F85">
+        <v>542.52867</v>
+      </c>
+      <c r="G85">
+        <v>41.2</v>
+      </c>
+      <c r="H85">
+        <v>653.1</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>41.7</v>
+      </c>
+      <c r="K85">
+        <v>17.2</v>
+      </c>
+      <c r="L85">
+        <v>24.5</v>
+      </c>
+      <c r="M85">
+        <v>129.555846396</v>
+      </c>
+      <c r="N85">
+        <v>-105.055846396</v>
+      </c>
+      <c r="O85">
+        <v>-36.76954623860001</v>
+      </c>
+      <c r="P85">
+        <v>-68.28630015740001</v>
+      </c>
+      <c r="Q85">
+        <v>-51.0863001574</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.9198329900648019</v>
+      </c>
+      <c r="T85">
+        <v>3.977540108841541</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.06618767302704101</v>
+      </c>
+      <c r="W85">
+        <v>0.2229943836811426</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1891076372201171</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3434569467663646</v>
+      </c>
+      <c r="C86">
+        <v>-189.2302893673506</v>
+      </c>
+      <c r="D86">
+        <v>318.6348706326494</v>
+      </c>
+      <c r="E86">
+        <v>548.51616</v>
+      </c>
+      <c r="F86">
+        <v>549.06516</v>
+      </c>
+      <c r="G86">
+        <v>41.2</v>
+      </c>
+      <c r="H86">
+        <v>653.1</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>41.7</v>
+      </c>
+      <c r="K86">
+        <v>17.2</v>
+      </c>
+      <c r="L86">
+        <v>24.5</v>
+      </c>
+      <c r="M86">
+        <v>131.116760208</v>
+      </c>
+      <c r="N86">
+        <v>-106.616760208</v>
+      </c>
+      <c r="O86">
+        <v>-37.31586607280001</v>
+      </c>
+      <c r="P86">
+        <v>-69.30089413520001</v>
+      </c>
+      <c r="Q86">
+        <v>-52.10089413520001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.9748975519438514</v>
+      </c>
+      <c r="T86">
+        <v>4.226136365644135</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.06539972453862386</v>
+      </c>
+      <c r="W86">
+        <v>0.2231825457801766</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1868563558246397</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3454569467663646</v>
+      </c>
+      <c r="C87">
+        <v>-197.8448987381497</v>
+      </c>
+      <c r="D87">
+        <v>316.5567512618503</v>
+      </c>
+      <c r="E87">
+        <v>555.05265</v>
+      </c>
+      <c r="F87">
+        <v>555.6016499999999</v>
+      </c>
+      <c r="G87">
+        <v>41.2</v>
+      </c>
+      <c r="H87">
+        <v>653.1</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>41.7</v>
+      </c>
+      <c r="K87">
+        <v>17.2</v>
+      </c>
+      <c r="L87">
+        <v>24.5</v>
+      </c>
+      <c r="M87">
+        <v>132.67767402</v>
+      </c>
+      <c r="N87">
+        <v>-108.17767402</v>
+      </c>
+      <c r="O87">
+        <v>-37.86218590699999</v>
+      </c>
+      <c r="P87">
+        <v>-70.31548811299999</v>
+      </c>
+      <c r="Q87">
+        <v>-53.11548811299998</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>1.037304055406775</v>
+      </c>
+      <c r="T87">
+        <v>4.507878790020412</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.06463031601464007</v>
+      </c>
+      <c r="W87">
+        <v>0.223366280535704</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1846580457561144</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3474569467663646</v>
+      </c>
+      <c r="C88">
+        <v>-206.4325769882653</v>
+      </c>
+      <c r="D88">
+        <v>314.5055630117348</v>
+      </c>
+      <c r="E88">
+        <v>561.58914</v>
+      </c>
+      <c r="F88">
+        <v>562.13814</v>
+      </c>
+      <c r="G88">
+        <v>41.2</v>
+      </c>
+      <c r="H88">
+        <v>653.1</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>41.7</v>
+      </c>
+      <c r="K88">
+        <v>17.2</v>
+      </c>
+      <c r="L88">
+        <v>24.5</v>
+      </c>
+      <c r="M88">
+        <v>134.238587832</v>
+      </c>
+      <c r="N88">
+        <v>-109.738587832</v>
+      </c>
+      <c r="O88">
+        <v>-38.4085057412</v>
+      </c>
+      <c r="P88">
+        <v>-71.3300820908</v>
+      </c>
+      <c r="Q88">
+        <v>-54.1300820908</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>1.108625773650116</v>
+      </c>
+      <c r="T88">
+        <v>4.829870132164727</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.06387880071214425</v>
+      </c>
+      <c r="W88">
+        <v>0.22354574238994</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1825108591775549</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3494569467663646</v>
+      </c>
+      <c r="C89">
+        <v>-214.9938442629114</v>
+      </c>
+      <c r="D89">
+        <v>312.4807857370886</v>
+      </c>
+      <c r="E89">
+        <v>568.12563</v>
+      </c>
+      <c r="F89">
+        <v>568.67463</v>
+      </c>
+      <c r="G89">
+        <v>41.2</v>
+      </c>
+      <c r="H89">
+        <v>653.1</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>41.7</v>
+      </c>
+      <c r="K89">
+        <v>17.2</v>
+      </c>
+      <c r="L89">
+        <v>24.5</v>
+      </c>
+      <c r="M89">
+        <v>135.799501644</v>
+      </c>
+      <c r="N89">
+        <v>-111.299501644</v>
+      </c>
+      <c r="O89">
+        <v>-38.9548255754</v>
+      </c>
+      <c r="P89">
+        <v>-72.34467606859999</v>
+      </c>
+      <c r="Q89">
+        <v>-55.14467606859999</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.190920063930894</v>
+      </c>
+      <c r="T89">
+        <v>5.201398603869706</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.06314456162349891</v>
+      </c>
+      <c r="W89">
+        <v>0.2237210786843085</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1804130332099969</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3514569467663646</v>
+      </c>
+      <c r="C90">
+        <v>-223.5292073982689</v>
+      </c>
+      <c r="D90">
+        <v>310.4819126017312</v>
+      </c>
+      <c r="E90">
+        <v>574.6621200000001</v>
+      </c>
+      <c r="F90">
+        <v>575.2111200000001</v>
+      </c>
+      <c r="G90">
+        <v>41.2</v>
+      </c>
+      <c r="H90">
+        <v>653.1</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>41.7</v>
+      </c>
+      <c r="K90">
+        <v>17.2</v>
+      </c>
+      <c r="L90">
+        <v>24.5</v>
+      </c>
+      <c r="M90">
+        <v>137.360415456</v>
+      </c>
+      <c r="N90">
+        <v>-112.860415456</v>
+      </c>
+      <c r="O90">
+        <v>-39.50114540960001</v>
+      </c>
+      <c r="P90">
+        <v>-73.35927004640001</v>
+      </c>
+      <c r="Q90">
+        <v>-56.15927004640001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.286930069258469</v>
+      </c>
+      <c r="T90">
+        <v>5.634848487525515</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.06242700978686822</v>
+      </c>
+      <c r="W90">
+        <v>0.2238924300628959</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1783628851053378</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3534569467663646</v>
+      </c>
+      <c r="C91">
+        <v>-232.0391603444549</v>
+      </c>
+      <c r="D91">
+        <v>308.5084496555451</v>
+      </c>
+      <c r="E91">
+        <v>581.19861</v>
+      </c>
+      <c r="F91">
+        <v>581.74761</v>
+      </c>
+      <c r="G91">
+        <v>41.2</v>
+      </c>
+      <c r="H91">
+        <v>653.1</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>41.7</v>
+      </c>
+      <c r="K91">
+        <v>17.2</v>
+      </c>
+      <c r="L91">
+        <v>24.5</v>
+      </c>
+      <c r="M91">
+        <v>138.921329268</v>
+      </c>
+      <c r="N91">
+        <v>-114.421329268</v>
+      </c>
+      <c r="O91">
+        <v>-40.0474652438</v>
+      </c>
+      <c r="P91">
+        <v>-74.37386402420002</v>
+      </c>
+      <c r="Q91">
+        <v>-57.17386402420001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.400396439191057</v>
+      </c>
+      <c r="T91">
+        <v>6.147107440936925</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.06172558271061129</v>
+      </c>
+      <c r="W91">
+        <v>0.224059930848706</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1763588077446037</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3554569467663646</v>
+      </c>
+      <c r="C92">
+        <v>-240.5241845724639</v>
+      </c>
+      <c r="D92">
+        <v>306.5599154275361</v>
+      </c>
+      <c r="E92">
+        <v>587.7351</v>
+      </c>
+      <c r="F92">
+        <v>588.2841</v>
+      </c>
+      <c r="G92">
+        <v>41.2</v>
+      </c>
+      <c r="H92">
+        <v>653.1</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>41.7</v>
+      </c>
+      <c r="K92">
+        <v>17.2</v>
+      </c>
+      <c r="L92">
+        <v>24.5</v>
+      </c>
+      <c r="M92">
+        <v>140.48224308</v>
+      </c>
+      <c r="N92">
+        <v>-115.98224308</v>
+      </c>
+      <c r="O92">
+        <v>-40.593785078</v>
+      </c>
+      <c r="P92">
+        <v>-75.38845800199999</v>
+      </c>
+      <c r="Q92">
+        <v>-58.18845800199999</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.536556083110163</v>
+      </c>
+      <c r="T92">
+        <v>6.761818185030618</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.06103974290271562</v>
+      </c>
+      <c r="W92">
+        <v>0.2242237093948315</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1743992654363303</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3574569467663646</v>
+      </c>
+      <c r="C93">
+        <v>-248.9847494657837</v>
+      </c>
+      <c r="D93">
+        <v>304.6358405342164</v>
+      </c>
+      <c r="E93">
+        <v>594.2715900000001</v>
+      </c>
+      <c r="F93">
+        <v>594.82059</v>
+      </c>
+      <c r="G93">
+        <v>41.2</v>
+      </c>
+      <c r="H93">
+        <v>653.1</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>41.7</v>
+      </c>
+      <c r="K93">
+        <v>17.2</v>
+      </c>
+      <c r="L93">
+        <v>24.5</v>
+      </c>
+      <c r="M93">
+        <v>142.043156892</v>
+      </c>
+      <c r="N93">
+        <v>-117.543156892</v>
+      </c>
+      <c r="O93">
+        <v>-41.1401049122</v>
+      </c>
+      <c r="P93">
+        <v>-76.40305197980001</v>
+      </c>
+      <c r="Q93">
+        <v>-59.20305197980001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.702973425677959</v>
+      </c>
+      <c r="T93">
+        <v>7.513131316700688</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.06036897649719126</v>
+      </c>
+      <c r="W93">
+        <v>0.2243838884124707</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1724827899919751</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3594569467663646</v>
+      </c>
+      <c r="C94">
+        <v>-257.4213126973558</v>
+      </c>
+      <c r="D94">
+        <v>302.7357673026442</v>
+      </c>
+      <c r="E94">
+        <v>600.80808</v>
+      </c>
+      <c r="F94">
+        <v>601.35708</v>
+      </c>
+      <c r="G94">
+        <v>41.2</v>
+      </c>
+      <c r="H94">
+        <v>653.1</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>41.7</v>
+      </c>
+      <c r="K94">
+        <v>17.2</v>
+      </c>
+      <c r="L94">
+        <v>24.5</v>
+      </c>
+      <c r="M94">
+        <v>143.604070704</v>
+      </c>
+      <c r="N94">
+        <v>-119.104070704</v>
+      </c>
+      <c r="O94">
+        <v>-41.6864247464</v>
+      </c>
+      <c r="P94">
+        <v>-77.4176459576</v>
+      </c>
+      <c r="Q94">
+        <v>-60.2176459576</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.910995103887704</v>
+      </c>
+      <c r="T94">
+        <v>8.452272731288277</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.05971279197004788</v>
+      </c>
+      <c r="W94">
+        <v>0.2245405852775526</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1706079770572797</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3614569467663646</v>
+      </c>
+      <c r="C95">
+        <v>-265.8343205925175</v>
+      </c>
+      <c r="D95">
+        <v>300.8592494074826</v>
+      </c>
+      <c r="E95">
+        <v>607.3445700000001</v>
+      </c>
+      <c r="F95">
+        <v>607.8935700000001</v>
+      </c>
+      <c r="G95">
+        <v>41.2</v>
+      </c>
+      <c r="H95">
+        <v>653.1</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>41.7</v>
+      </c>
+      <c r="K95">
+        <v>17.2</v>
+      </c>
+      <c r="L95">
+        <v>24.5</v>
+      </c>
+      <c r="M95">
+        <v>145.164984516</v>
+      </c>
+      <c r="N95">
+        <v>-120.664984516</v>
+      </c>
+      <c r="O95">
+        <v>-42.23274458060001</v>
+      </c>
+      <c r="P95">
+        <v>-78.43223993540002</v>
+      </c>
+      <c r="Q95">
+        <v>-61.23223993540002</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>2.178451547300234</v>
+      </c>
+      <c r="T95">
+        <v>9.659740264329459</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.05907071893811187</v>
+      </c>
+      <c r="W95">
+        <v>0.2246939123175789</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1687734826803197</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3634569467663646</v>
+      </c>
+      <c r="C96">
+        <v>-274.2242084785266</v>
+      </c>
+      <c r="D96">
+        <v>299.0058515214735</v>
+      </c>
+      <c r="E96">
+        <v>613.88106</v>
+      </c>
+      <c r="F96">
+        <v>614.43006</v>
+      </c>
+      <c r="G96">
+        <v>41.2</v>
+      </c>
+      <c r="H96">
+        <v>653.1</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>41.7</v>
+      </c>
+      <c r="K96">
+        <v>17.2</v>
+      </c>
+      <c r="L96">
+        <v>24.5</v>
+      </c>
+      <c r="M96">
+        <v>146.725898328</v>
+      </c>
+      <c r="N96">
+        <v>-122.225898328</v>
+      </c>
+      <c r="O96">
+        <v>-42.7790644148</v>
+      </c>
+      <c r="P96">
+        <v>-79.44683391320001</v>
+      </c>
+      <c r="Q96">
+        <v>-62.24683391320001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.53506013851694</v>
+      </c>
+      <c r="T96">
+        <v>11.26969697505104</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.05844230703451495</v>
+      </c>
+      <c r="W96">
+        <v>0.2248439770801579</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1669780200986142</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3654569467663647</v>
+      </c>
+      <c r="C97">
+        <v>-282.5914010212485</v>
+      </c>
+      <c r="D97">
+        <v>297.1751489787516</v>
+      </c>
+      <c r="E97">
+        <v>620.4175500000001</v>
+      </c>
+      <c r="F97">
+        <v>620.9665500000001</v>
+      </c>
+      <c r="G97">
+        <v>41.2</v>
+      </c>
+      <c r="H97">
+        <v>653.1</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>41.7</v>
+      </c>
+      <c r="K97">
+        <v>17.2</v>
+      </c>
+      <c r="L97">
+        <v>24.5</v>
+      </c>
+      <c r="M97">
+        <v>148.28681214</v>
+      </c>
+      <c r="N97">
+        <v>-123.78681214</v>
+      </c>
+      <c r="O97">
+        <v>-43.325384249</v>
+      </c>
+      <c r="P97">
+        <v>-80.46142789100003</v>
+      </c>
+      <c r="Q97">
+        <v>-63.26142789100003</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>3.03431216622033</v>
+      </c>
+      <c r="T97">
+        <v>13.52363637006125</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.05782712485520426</v>
+      </c>
+      <c r="W97">
+        <v>0.2249908825845773</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.165220356729155</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3674569467663646</v>
+      </c>
+      <c r="C98">
+        <v>-290.9363125495479</v>
+      </c>
+      <c r="D98">
+        <v>295.366727450452</v>
+      </c>
+      <c r="E98">
+        <v>626.95404</v>
+      </c>
+      <c r="F98">
+        <v>627.5030399999999</v>
+      </c>
+      <c r="G98">
+        <v>41.2</v>
+      </c>
+      <c r="H98">
+        <v>653.1</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>41.7</v>
+      </c>
+      <c r="K98">
+        <v>17.2</v>
+      </c>
+      <c r="L98">
+        <v>24.5</v>
+      </c>
+      <c r="M98">
+        <v>149.847725952</v>
+      </c>
+      <c r="N98">
+        <v>-125.347725952</v>
+      </c>
+      <c r="O98">
+        <v>-43.87170408319999</v>
+      </c>
+      <c r="P98">
+        <v>-81.47602186879999</v>
+      </c>
+      <c r="Q98">
+        <v>-64.27602186879999</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>3.783190207775403</v>
+      </c>
+      <c r="T98">
+        <v>16.90454546257653</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.05722475897129589</v>
+      </c>
+      <c r="W98">
+        <v>0.2251347275576546</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1634993113465597</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3694569467663646</v>
+      </c>
+      <c r="C99">
+        <v>-299.2593473679102</v>
+      </c>
+      <c r="D99">
+        <v>293.5801826320898</v>
+      </c>
+      <c r="E99">
+        <v>633.49053</v>
+      </c>
+      <c r="F99">
+        <v>634.03953</v>
+      </c>
+      <c r="G99">
+        <v>41.2</v>
+      </c>
+      <c r="H99">
+        <v>653.1</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>41.7</v>
+      </c>
+      <c r="K99">
+        <v>17.2</v>
+      </c>
+      <c r="L99">
+        <v>24.5</v>
+      </c>
+      <c r="M99">
+        <v>151.408639764</v>
+      </c>
+      <c r="N99">
+        <v>-126.908639764</v>
+      </c>
+      <c r="O99">
+        <v>-44.4180239174</v>
+      </c>
+      <c r="P99">
+        <v>-82.49061584660001</v>
+      </c>
+      <c r="Q99">
+        <v>-65.29061584660001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>5.031320277033872</v>
+      </c>
+      <c r="T99">
+        <v>22.53939395010204</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.05663481300251964</v>
+      </c>
+      <c r="W99">
+        <v>0.2252756066549983</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1618137514357704</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3714569467663646</v>
+      </c>
+      <c r="C100">
+        <v>-307.5609000577826</v>
+      </c>
+      <c r="D100">
+        <v>291.8151199422174</v>
+      </c>
+      <c r="E100">
+        <v>640.02702</v>
+      </c>
+      <c r="F100">
+        <v>640.57602</v>
+      </c>
+      <c r="G100">
+        <v>41.2</v>
+      </c>
+      <c r="H100">
+        <v>653.1</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>41.7</v>
+      </c>
+      <c r="K100">
+        <v>17.2</v>
+      </c>
+      <c r="L100">
+        <v>24.5</v>
+      </c>
+      <c r="M100">
+        <v>152.969553576</v>
+      </c>
+      <c r="N100">
+        <v>-128.469553576</v>
+      </c>
+      <c r="O100">
+        <v>-44.9643437516</v>
+      </c>
+      <c r="P100">
+        <v>-83.50520982440001</v>
+      </c>
+      <c r="Q100">
+        <v>-66.30520982440001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>7.527580415550807</v>
+      </c>
+      <c r="T100">
+        <v>33.80909092515306</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.05605690674739189</v>
+      </c>
+      <c r="W100">
+        <v>0.2254136106687228</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1601625907068339</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3734569467663647</v>
+      </c>
+      <c r="C101">
+        <v>-315.8413557681131</v>
+      </c>
+      <c r="D101">
+        <v>290.071154231887</v>
+      </c>
+      <c r="E101">
+        <v>646.5635100000001</v>
+      </c>
+      <c r="F101">
+        <v>647.11251</v>
+      </c>
+      <c r="G101">
+        <v>41.2</v>
+      </c>
+      <c r="H101">
+        <v>653.1</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>41.7</v>
+      </c>
+      <c r="K101">
+        <v>17.2</v>
+      </c>
+      <c r="L101">
+        <v>24.5</v>
+      </c>
+      <c r="M101">
+        <v>154.530467388</v>
+      </c>
+      <c r="N101">
+        <v>-130.030467388</v>
+      </c>
+      <c r="O101">
+        <v>-45.5106635858</v>
+      </c>
+      <c r="P101">
+        <v>-84.51980380220002</v>
+      </c>
+      <c r="Q101">
+        <v>-67.31980380220001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>15.01636083110161</v>
+      </c>
+      <c r="T101">
+        <v>67.61818185030612</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.05549067536610509</v>
+      </c>
+      <c r="W101">
+        <v>0.2255488267225741</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1585447867603003</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
